--- a/algorithms/1-ga_sa_hybrid/v2/logs/FSTG_EXCEL_PREMIUM_FUSED.xlsx
+++ b/algorithms/1-ga_sa_hybrid/v2/logs/FSTG_EXCEL_PREMIUM_FUSED.xlsx
@@ -134,12 +134,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F3F4"/>
+        <fgColor rgb="00ECF0F1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECF0F1"/>
+        <fgColor rgb="00F2F3F4"/>
       </patternFill>
     </fill>
   </fills>
@@ -183,32 +183,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -220,36 +220,36 @@
     <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -820,16 +820,16 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Développement Personnel
+          <t>Physiologie Animale et Végétale
 (CM - Amphi 1)
-Section: GEG S4</t>
+Section: GB S4</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Analyse Numérique
+          <t>Mecanique du point / Optique
 (CM - Amphi 2)
-Section: GI S4</t>
+Section: MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="D4" s="7" t="n"/>
@@ -846,54 +846,60 @@
       <c r="O4" s="7" t="n"/>
       <c r="P4" s="7" t="n"/>
       <c r="Q4" s="7" t="n"/>
-      <c r="R4" s="7" t="n"/>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
+        <is>
+          <t>Electricité
+(TD - Salle 23)
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="S4" s="9" t="inlineStr">
         <is>
           <t>Langue Etrangère 2
 (TD - Salle 24)
+GB-GEG S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="T4" s="10" t="inlineStr">
+        <is>
+          <t>Bases de Données
+(TD - Salle 25)
+GB-GEG S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="U4" s="11" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 26)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="V4" s="12" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 27)
 GP-GI S2 - Groupe: 3</t>
         </is>
       </c>
-      <c r="T4" s="9" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 25)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="U4" s="10" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 26)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>Langue Etrangère 2
-(TD - Salle 27)
-MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="W4" s="11" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
 (TD - Salle 28)
-GB-GEG S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="X4" s="12" t="inlineStr">
-        <is>
-          <t>Structure de la matière
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="X4" s="13" t="inlineStr">
+        <is>
+          <t>Systèmes d'Information et Bases de Données
 (TD - Salle 29)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="Y4" s="13" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
+GI S4 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="Y4" s="14" t="inlineStr">
+        <is>
+          <t>Structure des Données
 (TD - Salle 30)
-GB-GEG S2 - Groupe: 2</t>
+GI S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="Z4" s="7" t="n"/>
@@ -909,19 +915,25 @@
         </is>
       </c>
       <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Métrologie Capteurs
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Optique Physique
+(CM - Amphi 2)
+Section: GP S4</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Biochimie Métabolique et Enzymologie
 (CM - Amphi 3)
-Section: GESE S4</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
+Section: GB S4</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Systèmes d'Information et Bases de Données
 (CM - Amphi 4)
-Section: GP-GI S2</t>
+Section: GI S4</t>
         </is>
       </c>
       <c r="F5" s="7" t="n"/>
@@ -936,60 +948,60 @@
       <c r="O5" s="7" t="n"/>
       <c r="P5" s="7" t="n"/>
       <c r="Q5" s="7" t="n"/>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>Développement Personnel
+      <c r="R5" s="15" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
 (TD - Salle 23)
-GP S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="S5" s="8" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
+GB-GEG S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="S5" s="9" t="inlineStr">
+        <is>
+          <t>Culture digitale
 (TD - Salle 24)
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="T5" s="9" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 25)
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
+(TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="V5" s="9" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 27)
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="W5" s="10" t="inlineStr">
+        <is>
+          <t>Bases de Données
+(TD - Salle 28)
 GB-GEG S2 - Groupe: 4</t>
         </is>
       </c>
-      <c r="T5" s="14" t="inlineStr">
-        <is>
-          <t>Méthodes d'analyse
-(TD - Salle 25)
-GB S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="U5" s="10" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(TD - Salle 26)
-GI S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>Analyse de Données
-(TD - Salle 27)
-GEG S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>Systèmes d'Information et Bases de Données
-(TD - Salle 28)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="X5" s="15" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
+      <c r="X5" s="9" t="inlineStr">
+        <is>
+          <t>Culture digitale
 (TD - Salle 29)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="Y5" s="6" t="inlineStr">
-        <is>
-          <t>Analyse 2
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="Y5" s="5" t="inlineStr">
+        <is>
+          <t>Éléments de Génie Chimique
 (TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 5</t>
+GC S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="Z5" s="7" t="n"/>
@@ -1004,14 +1016,20 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Structure de la matière
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Analyse 2
 (CM - Amphi 1)
-Section: MSD-GC-GESE S2</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n"/>
+Section: GP-GI S2</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(CM - Amphi 2)
+Section: GB S4</t>
+        </is>
+      </c>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
@@ -1026,54 +1044,42 @@
       <c r="O6" s="7" t="n"/>
       <c r="P6" s="7" t="n"/>
       <c r="Q6" s="7" t="n"/>
-      <c r="R6" s="5" t="inlineStr">
+      <c r="R6" s="12" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 23)
+MSD S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="n"/>
+      <c r="T6" s="10" t="inlineStr">
         <is>
           <t>Bases de Données
-(TD - Salle 23)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="S6" s="15" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
-(TD - Salle 24)
+(TD - Salle 25)
 GB-GEG S2 - Groupe: 3</t>
         </is>
       </c>
-      <c r="T6" s="7" t="n"/>
-      <c r="U6" s="10" t="inlineStr">
-        <is>
-          <t>Algèbre 2
+      <c r="U6" s="11" t="inlineStr">
+        <is>
+          <t>Analyse 2
 (TD - Salle 26)
-GP-GI S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="V6" s="9" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 27)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="W6" s="11" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
+MSD-GC-GESE S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="n"/>
+      <c r="W6" s="9" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
 (TD - Salle 28)
 GB-GEG S2 - Groupe: 2</t>
         </is>
       </c>
-      <c r="X6" s="12" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 29)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="Y6" s="13" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
+      <c r="X6" s="7" t="n"/>
+      <c r="Y6" s="8" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
 (TD - Salle 30)
-GP-GI S2 - Groupe: 1</t>
+GB-GEG S2 - Groupe: 1</t>
         </is>
       </c>
       <c r="Z6" s="7" t="n"/>
@@ -1088,26 +1094,26 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Algèbre 2
 (CM - Amphi 1)
 Section: GP-GI S2</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>Chimie Minérale 2
-(CM - Amphi 3)
-Section: GC S4</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>Inférence Statistique et Applications
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
+(CM - Amphi 2)
+Section: MSD-GC-GESE S2</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
 (CM - Amphi 4)
-Section: MSD S4</t>
+Section: GB-GEG S2</t>
         </is>
       </c>
       <c r="F7" s="7" t="n"/>
@@ -1122,60 +1128,60 @@
       <c r="O7" s="7" t="n"/>
       <c r="P7" s="7" t="n"/>
       <c r="Q7" s="7" t="n"/>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>Physiologie Animale et Végétale
 (TD - Salle 23)
+GB S4 - Groupe:</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>Chimie Minérale 2
+(TD - Salle 24)
+GC S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="T7" s="15" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
+(TD - Salle 25)
 GP S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="S7" s="12" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 24)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 25)
-GB-GEG S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="U7" s="13" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
+      <c r="U7" s="10" t="inlineStr">
+        <is>
+          <t>Biochimie Métabolique et Enzymologie
 (TD - Salle 26)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="V7" s="6" t="inlineStr">
-        <is>
-          <t>Analyse 2
+GB S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="V7" s="14" t="inlineStr">
+        <is>
+          <t>Recherche Opérationnelle
 (TD - Salle 27)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="W7" s="11" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
+GI S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="W7" s="12" t="inlineStr">
+        <is>
+          <t>LTC2 Français
 (TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="X7" s="15" t="inlineStr">
-        <is>
-          <t>Programmation Web
+GI S4 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="X7" s="13" t="inlineStr">
+        <is>
+          <t>Systèmes d'Information et Bases de Données
 (TD - Salle 29)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="Y7" s="5" t="inlineStr">
-        <is>
-          <t>Développement Personnel
+GI S4 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="Y7" s="13" t="inlineStr">
+        <is>
+          <t>Méthodes d'analyse
 (TD - Salle 30)
-GESE S4 - Groupe: 1</t>
+GEG S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="Z7" s="7" t="n"/>
@@ -1190,20 +1196,20 @@
           <t>16:35</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
-(CM - Amphi 1)
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
+(CM - Amphi 2)
+Section: GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(CM - Amphi 4)
 Section: GP-GI S2</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
-(CM - Amphi 4)
-Section: GB-GEG S2</t>
         </is>
       </c>
       <c r="F8" s="7" t="n"/>
@@ -1218,60 +1224,60 @@
       <c r="O8" s="7" t="n"/>
       <c r="P8" s="7" t="n"/>
       <c r="Q8" s="7" t="n"/>
-      <c r="R8" s="5" t="inlineStr">
-        <is>
-          <t>Développement Personnel
+      <c r="R8" s="12" t="inlineStr">
+        <is>
+          <t>Algèbre 2
 (TD - Salle 23)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="S8" s="11" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>Biologie Moléculaire et Génétique
 (TD - Salle 24)
+GB S4 - Groupe:</t>
+        </is>
+      </c>
+      <c r="T8" s="9" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 25)
 MSD-GC-GESE S2 - Groupe: 6</t>
         </is>
       </c>
-      <c r="T8" s="10" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(TD - Salle 25)
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(TD - Salle 26)
 GC S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="U8" s="9" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 26)
+      <c r="V8" s="6" t="inlineStr">
+        <is>
+          <t>Optique Physique
+(TD - Salle 27)
+GP S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="W8" s="9" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 28)
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="X8" s="11" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
+(TD - Salle 29)
 MSD-GC-GESE S2 - Groupe: 4</t>
         </is>
       </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>Analyse de Données
-(TD - Salle 27)
-GB S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
-        <is>
-          <t>Structure des Données
-(TD - Salle 28)
-GI S4 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="X8" s="12" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 29)
-MSD-GC-GESE S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="Y8" s="5" t="inlineStr">
-        <is>
-          <t>Développement Personnel
+      <c r="Y8" s="6" t="inlineStr">
+        <is>
+          <t>Géomatique
 (TD - Salle 30)
-MSD S4 - Groupe: 1</t>
+GEG S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="Z8" s="7" t="n"/>
@@ -1293,22 +1299,22 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Analyse 2
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
 (CM - Amphi 1)
-Section: MSD-GC-GESE S2</t>
+Section: GP-GI S2</t>
         </is>
       </c>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Géologie Structurale
-(CM - Amphi 3)
-Section: GEG S4</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Biologie Moléculaire et Génétique
+(CM - Amphi 4)
+Section: GB S4</t>
+        </is>
+      </c>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="n"/>
@@ -1321,54 +1327,60 @@
       <c r="O10" s="7" t="n"/>
       <c r="P10" s="7" t="n"/>
       <c r="Q10" s="7" t="n"/>
-      <c r="R10" s="5" t="inlineStr">
-        <is>
-          <t>Bases de Données
+      <c r="R10" s="12" t="inlineStr">
+        <is>
+          <t>Algèbre 2
 (TD - Salle 23)
-GB-GEG S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="S10" s="12" t="inlineStr">
+MSD-GC-GESE S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="S10" s="9" t="inlineStr">
         <is>
           <t>Structure de la matière
 (TD - Salle 24)
-GP-GI S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="T10" s="9" t="inlineStr">
+        <is>
+          <t>Structure de la matière
 (TD - Salle 25)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="U10" s="10" t="inlineStr">
-        <is>
-          <t>Algèbre 2
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="U10" s="14" t="inlineStr">
+        <is>
+          <t>Développement Personnel
 (TD - Salle 26)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="V10" s="12" t="inlineStr">
-        <is>
-          <t>Métrologie Capteurs
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="V10" s="5" t="inlineStr">
+        <is>
+          <t>Analyse de Données
 (TD - Salle 27)
-GESE S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="W10" s="7" t="n"/>
+MSD S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="W10" s="15" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
+(TD - Salle 28)
+GB-GEG S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="X10" s="11" t="inlineStr">
         <is>
-          <t>Mécanique des Fluides et Transfert Thermique
+          <t>Thermodynamique Chimique et Cinétique
 (TD - Salle 29)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="Y10" s="5" t="inlineStr">
-        <is>
-          <t>Développement Personnel
+GC S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="Y10" s="8" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
 (TD - Salle 30)
-GC S4 - Groupe: 1</t>
+GB-GEG S2 - Groupe: 4</t>
         </is>
       </c>
       <c r="Z10" s="7" t="n"/>
@@ -1383,32 +1395,26 @@
           <t>10:35</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Analyse 2
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Algèbre 2
 (CM - Amphi 1)
+Section: MSD-GC-GESE S2</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Géomatique
+(CM - Amphi 2)
+Section: GEG S4</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(CM - Amphi 4)
 Section: GP-GI S2</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
-(CM - Amphi 2)
-Section: MSD S4</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Éléments de Génie Chimique
-(CM - Amphi 3)
-Section: GC S4</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Automatique
-(CM - Amphi 4)
-Section: GESE S4</t>
         </is>
       </c>
       <c r="F11" s="7" t="n"/>
@@ -1423,60 +1429,60 @@
       <c r="O11" s="7" t="n"/>
       <c r="P11" s="7" t="n"/>
       <c r="Q11" s="7" t="n"/>
-      <c r="R11" s="8" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>Physiologie Animale et Végétale
 (TD - Salle 23)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="S11" s="6" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
+GB S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="S11" s="14" t="inlineStr">
+        <is>
+          <t>Développement Personnel
 (TD - Salle 24)
+GP S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="T11" s="15" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
+(TD - Salle 25)
+GB-GEG S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="U11" s="9" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 26)
+GB-GEG S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="V11" s="13" t="inlineStr">
+        <is>
+          <t>Electrotechnique
+(TD - Salle 27)
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="W11" s="14" t="inlineStr">
+        <is>
+          <t>Recherche Opérationnelle
+(TD - Salle 28)
+GI S4 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="X11" s="13" t="inlineStr">
+        <is>
+          <t>Systèmes d'Information et Bases de Données
+(TD - Salle 29)
 GI S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="T11" s="9" t="inlineStr">
-        <is>
-          <t>Pétrographie et Minéralogie
-(TD - Salle 25)
-GEG S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="U11" s="5" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
-(TD - Salle 26)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 27)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="W11" s="8" t="inlineStr">
-        <is>
-          <t>Structure des Données
-(TD - Salle 28)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="X11" s="5" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="Y11" s="13" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
+      <c r="Y11" s="15" t="inlineStr">
+        <is>
+          <t>Inférence Statistique et Applications
 (TD - Salle 30)
-GB-GEG S2 - Groupe: 3</t>
+MSD S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="Z11" s="7" t="n"/>
@@ -1492,11 +1498,11 @@
         </is>
       </c>
       <c r="B12" s="7" t="n"/>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>LTC2 Français
 (CM - Amphi 2)
-Section: GB-GEG S2</t>
+Section: GI S4</t>
         </is>
       </c>
       <c r="D12" s="7" t="n"/>
@@ -1513,62 +1519,56 @@
       <c r="O12" s="7" t="n"/>
       <c r="P12" s="7" t="n"/>
       <c r="Q12" s="7" t="n"/>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="12" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 23)
+GB S4 - Groupe:</t>
+        </is>
+      </c>
+      <c r="S12" s="15" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
+(TD - Salle 24)
+GB-GEG S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="T12" s="10" t="inlineStr">
+        <is>
+          <t>Bases de Données
+(TD - Salle 25)
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="U12" s="9" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 26)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="V12" s="11" t="inlineStr">
         <is>
           <t>Analyse 2
-(TD - Salle 23)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="S12" s="11" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
-(TD - Salle 24)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="T12" s="11" t="inlineStr">
-        <is>
-          <t>Analyse 4
-(TD - Salle 25)
-GP S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="U12" s="13" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
-(TD - Salle 26)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="V12" s="14" t="inlineStr">
-        <is>
-          <t>Electricité
 (TD - Salle 27)
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="W12" s="15" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
+(TD - Salle 28)
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="X12" s="11" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 29)
 GP-GI S2 - Groupe: 1</t>
         </is>
       </c>
-      <c r="W12" s="11" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
-(TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="X12" s="9" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 29)
-MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="Y12" s="5" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
-(TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 2</t>
-        </is>
-      </c>
+      <c r="Y12" s="7" t="n"/>
       <c r="Z12" s="7" t="n"/>
       <c r="AA12" s="7" t="n"/>
       <c r="AB12" s="7" t="n"/>
@@ -1582,21 +1582,15 @@
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Culture digitale
-(CM - Amphi 2)
+(CM - Amphi 4)
 Section: MSD-GC-GESE S2</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Biologie Moléculaire et Génétique
-(CM - Amphi 3)
-Section: GB S4</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
       <c r="H13" s="7" t="n"/>
@@ -1609,54 +1603,60 @@
       <c r="O13" s="7" t="n"/>
       <c r="P13" s="7" t="n"/>
       <c r="Q13" s="7" t="n"/>
-      <c r="R13" s="7" t="n"/>
-      <c r="S13" s="15" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
+      <c r="R13" s="9" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 23)
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="S13" s="14" t="inlineStr">
+        <is>
+          <t>Développement Personnel
 (TD - Salle 24)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="T13" s="10" t="inlineStr">
-        <is>
-          <t>Recherche Opérationnelle
+GI S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="T13" s="15" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
 (TD - Salle 25)
-GI S4 - Groupe: 1</t>
+GB-GEG S2 - Groupe: 6</t>
         </is>
       </c>
       <c r="U13" s="10" t="inlineStr">
         <is>
-          <t>Chimie Minérale 2
+          <t>Biochimie Métabolique et Enzymologie
 (TD - Salle 26)
+GB S4 - Groupe:</t>
+        </is>
+      </c>
+      <c r="V13" s="9" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 27)
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
+(TD - Salle 28)
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="X13" s="13" t="inlineStr">
+        <is>
+          <t>Méthodes d'analyse
+(TD - Salle 29)
+GB S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="Y13" s="10" t="inlineStr">
+        <is>
+          <t>Chimie Organique 2
+(TD - Salle 30)
 GC S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 27)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 28)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="X13" s="5" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="Y13" s="5" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(TD - Salle 30)
-GEG S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="Z13" s="7" t="n"/>
@@ -1671,20 +1671,14 @@
           <t>16:35</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Chimie Minérale 2
 (CM - Amphi 1)
-Section: MSD-GC-GESE S2</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(CM - Amphi 2)
-Section: GP-GI S2</t>
-        </is>
-      </c>
+Section: GC S4</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n"/>
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
@@ -1699,54 +1693,60 @@
       <c r="O14" s="7" t="n"/>
       <c r="P14" s="7" t="n"/>
       <c r="Q14" s="7" t="n"/>
-      <c r="R14" s="8" t="inlineStr">
-        <is>
-          <t>Structure des Données
+      <c r="R14" s="12" t="inlineStr">
+        <is>
+          <t>LTC2 Français
 (TD - Salle 23)
-GI S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="S14" s="6" t="inlineStr">
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr">
         <is>
           <t>Analyse Numérique
 (TD - Salle 24)
-GI S4 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="T14" s="10" t="inlineStr">
-        <is>
-          <t>Recherche Opérationnelle
+GI S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="T14" s="14" t="inlineStr">
+        <is>
+          <t>Développement Personnel
 (TD - Salle 25)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="U14" s="13" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
+GB S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="U14" s="15" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
 (TD - Salle 26)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="V14" s="7" t="n"/>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>Systèmes d'Information et Bases de Données
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="V14" s="12" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 27)
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t>Electricité
 (TD - Salle 28)
-MSD S4 - Groupe: 1</t>
+GP-GI S2 - Groupe: 2</t>
         </is>
       </c>
       <c r="X14" s="15" t="inlineStr">
         <is>
-          <t>Réactivité Chimique
+          <t>Géodynamique externe
 (TD - Salle 29)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="Y14" s="5" t="inlineStr">
-        <is>
-          <t>Développement Personnel
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="Y14" s="9" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
 (TD - Salle 30)
-GB S4 - Groupe: 1</t>
+GP-GI S2 - Groupe: 6</t>
         </is>
       </c>
       <c r="Z14" s="7" t="n"/>
@@ -1768,21 +1768,27 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Bases de Données
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Méthodes d'analyse
 (CM - Amphi 1)
-Section: GB-GEG S2</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Recherche Opérationnelle
+Section: GB S4</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
 (CM - Amphi 2)
 Section: GI S4</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(CM - Amphi 3)
+Section: GC S4</t>
+        </is>
+      </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -1796,54 +1802,60 @@
       <c r="O16" s="7" t="n"/>
       <c r="P16" s="7" t="n"/>
       <c r="Q16" s="7" t="n"/>
-      <c r="R16" s="7" t="n"/>
+      <c r="R16" s="8" t="inlineStr">
+        <is>
+          <t>Electricité
+(TD - Salle 23)
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="S16" s="12" t="inlineStr">
         <is>
-          <t>Structure de la matière
+          <t>Algèbre 2
 (TD - Salle 24)
-MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="T16" s="10" t="inlineStr">
+MSD-GC-GESE S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="T16" s="9" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 25)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="U16" s="9" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 26)
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="V16" s="12" t="inlineStr">
         <is>
           <t>Algèbre 2
-(TD - Salle 25)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="U16" s="13" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
-(TD - Salle 26)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>Analyse de Données
 (TD - Salle 27)
-MSD S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="W16" s="12" t="inlineStr">
-        <is>
-          <t>Physiologie Animale et Végétale
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
 (TD - Salle 28)
-GB S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="X16" s="14" t="inlineStr">
-        <is>
-          <t>Méthodes d'analyse
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="X16" s="11" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
 (TD - Salle 29)
-GEG S4 - Groupe: 1</t>
+MSD-GC-GESE S2 - Groupe: 1</t>
         </is>
       </c>
       <c r="Y16" s="6" t="inlineStr">
         <is>
-          <t>Analyse 2
+          <t>Biologie Animale et Végétale
 (TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 2</t>
+GB-GEG S2 - Groupe: 1</t>
         </is>
       </c>
       <c r="Z16" s="7" t="n"/>
@@ -1858,34 +1870,22 @@
           <t>10:35</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Éléments de Génie Chimique
 (CM - Amphi 1)
-Section: GB-GEG S2</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
-(CM - Amphi 2)
-Section: GESE S4</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
+Section: GC S4</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Analyse de Données
 (CM - Amphi 3)
-Section: MSD S4</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>Optique Physique
-(CM - Amphi 4)
-Section: GP S4</t>
-        </is>
-      </c>
+Section: GB S4</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
       <c r="H17" s="7" t="n"/>
@@ -1900,54 +1900,60 @@
       <c r="Q17" s="7" t="n"/>
       <c r="R17" s="8" t="inlineStr">
         <is>
-          <t>Langue Etrangère 2
+          <t>Electricité
 (TD - Salle 23)
-MSD-GC-GESE S2 - Groupe: 2</t>
+GP-GI S2 - Groupe: 4</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>Développement Personnel
+          <t>Analyse 4
 (TD - Salle 24)
-GI S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
+GP S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="T17" s="15" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
 (TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="U17" s="10" t="inlineStr">
+GB-GEG S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="U17" s="12" t="inlineStr">
         <is>
           <t>LTC2 Français
 (TD - Salle 26)
-GB S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr">
+GI S4 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="V17" s="11" t="inlineStr">
         <is>
           <t>Analyse 2
 (TD - Salle 27)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="W17" s="10" t="inlineStr">
-        <is>
-          <t>Algèbre 2
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="W17" s="12" t="inlineStr">
+        <is>
+          <t>LTC2 Français
 (TD - Salle 28)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="X17" s="15" t="inlineStr">
-        <is>
-          <t>Programmation Web
+GI S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="X17" s="12" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
 (TD - Salle 29)
-GI S4 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="Y17" s="7" t="n"/>
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="Y17" s="9" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 30)
+MSD-GC-GESE S2 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="Z17" s="7" t="n"/>
       <c r="AA17" s="7" t="n"/>
       <c r="AB17" s="7" t="n"/>
@@ -1960,14 +1966,20 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n"/>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(CM - Amphi 1)
+Section: GB S4</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Electricité
 (CM - Amphi 4)
-Section: MSD-GC-GESE S2</t>
+Section: GP-GI S2</t>
         </is>
       </c>
       <c r="F18" s="7" t="n"/>
@@ -1982,60 +1994,36 @@
       <c r="O18" s="7" t="n"/>
       <c r="P18" s="7" t="n"/>
       <c r="Q18" s="7" t="n"/>
-      <c r="R18" s="8" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 23)
-GB-GEG S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="S18" s="8" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
+      <c r="R18" s="7" t="n"/>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
 (TD - Salle 24)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
 (TD - Salle 25)
-GP-GI S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="U18" s="9" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 26)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
+MSD-GC-GESE S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="U18" s="7" t="n"/>
       <c r="V18" s="9" t="inlineStr">
         <is>
           <t>Culture digitale
 (TD - Salle 27)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="W18" s="15" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
-(TD - Salle 28)
-GB-GEG S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="X18" s="11" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="Y18" s="12" t="inlineStr">
-        <is>
-          <t>Structure de la matière
+GB-GEG S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="W18" s="7" t="n"/>
+      <c r="X18" s="7" t="n"/>
+      <c r="Y18" s="6" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
 (TD - Salle 30)
-GP-GI S2 - Groupe: 3</t>
+GB-GEG S2 - Groupe: 2</t>
         </is>
       </c>
       <c r="Z18" s="7" t="n"/>
@@ -2050,32 +2038,26 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
-(CM - Amphi 1)
-Section: GP S4</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Analyse 4
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
 (CM - Amphi 2)
+Section: GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(CM - Amphi 3)
 Section: MSD S4</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Géomatique
-(CM - Amphi 3)
-Section: GEG S4</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>Biochimie Métabolique et Enzymologie
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Chimie Organique 2
 (CM - Amphi 4)
-Section: GB S4</t>
+Section: GC S4</t>
         </is>
       </c>
       <c r="F19" s="7" t="n"/>
@@ -2090,60 +2072,60 @@
       <c r="O19" s="7" t="n"/>
       <c r="P19" s="7" t="n"/>
       <c r="Q19" s="7" t="n"/>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R19" s="12" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 23)
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(TD - Salle 24)
+GB S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="T19" s="9" t="inlineStr">
         <is>
           <t>Analyse Numérique
-(TD - Salle 23)
+(TD - Salle 25)
+GP S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="U19" s="6" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
+(TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="V19" s="12" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 27)
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 28)
+MSD-GC-GESE S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="X19" s="11" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
+(TD - Salle 29)
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="Y19" s="8" t="inlineStr">
+        <is>
+          <t>Programmation Web
+(TD - Salle 30)
 GI S4 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="S19" s="13" t="inlineStr">
-        <is>
-          <t>Éléments de Génie Chimique
-(TD - Salle 24)
-GC S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="T19" s="9" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 25)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="U19" s="10" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 26)
-MSD-GC-GESE S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 27)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t>Structure des Données
-(TD - Salle 28)
-GESE S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="X19" s="9" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 29)
-GP-GI S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="Y19" s="12" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 4</t>
         </is>
       </c>
       <c r="Z19" s="7" t="n"/>
@@ -2158,22 +2140,28 @@
           <t>16:35</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>Structure de la matière
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Thermodynamique Chimique et Cinétique
 (CM - Amphi 1)
-Section: GP-GI S2</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Analyse de Données
-(CM - Amphi 3)
 Section: GC S4</t>
         </is>
       </c>
-      <c r="E20" s="7" t="n"/>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Structure des Données
+(CM - Amphi 2)
+Section: GI S4</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(CM - Amphi 4)
+Section: GB-GEG S2</t>
+        </is>
+      </c>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="7" t="n"/>
@@ -2186,60 +2174,60 @@
       <c r="O20" s="7" t="n"/>
       <c r="P20" s="7" t="n"/>
       <c r="Q20" s="7" t="n"/>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
+      <c r="R20" s="12" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
 (TD - Salle 23)
-GESE S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="S20" s="15" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>Analyse 4
 (TD - Salle 24)
-GB-GEG S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="T20" s="10" t="inlineStr">
-        <is>
-          <t>Recherche Opérationnelle
+MSD S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="T20" s="9" t="inlineStr">
+        <is>
+          <t>Structure de la matière
 (TD - Salle 25)
-GI S4 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="U20" s="13" t="inlineStr">
-        <is>
-          <t>Biochimie Métabolique et Enzymologie
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="U20" s="6" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
 (TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="V20" s="13" t="inlineStr">
+        <is>
+          <t>Méthodes d'analyse
+(TD - Salle 27)
+GB S4 - Groupe:</t>
+        </is>
+      </c>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 28)
+MSD-GC-GESE S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="X20" s="11" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 29)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="Y20" s="12" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 30)
 GB S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V20" s="6" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 27)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="W20" s="15" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
-(TD - Salle 28)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="X20" s="5" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="Y20" s="5" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
-(TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 5</t>
         </is>
       </c>
       <c r="Z20" s="7" t="n"/>
@@ -2261,16 +2249,22 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(CM - Amphi 2)
-Section: GB-GEG S2</t>
-        </is>
-      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(CM - Amphi 1)
+Section: MSD-GC-GESE S2</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(CM - Amphi 4)
+Section: GP-GI S2</t>
+        </is>
+      </c>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
@@ -2283,60 +2277,60 @@
       <c r="O22" s="7" t="n"/>
       <c r="P22" s="7" t="n"/>
       <c r="Q22" s="7" t="n"/>
-      <c r="R22" s="8" t="inlineStr">
+      <c r="R22" s="9" t="inlineStr">
         <is>
           <t>Langue Etrangère 2
 (TD - Salle 23)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="S22" s="5" t="inlineStr">
-        <is>
-          <t>Développement Personnel
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="S22" s="12" t="inlineStr">
+        <is>
+          <t>Automatique
 (TD - Salle 24)
-GI S4 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="T22" s="10" t="inlineStr">
-        <is>
-          <t>Algèbre 2
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="T22" s="15" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
 (TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="U22" s="6" t="inlineStr">
-        <is>
-          <t>Analyse 2
+GB-GEG S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="U22" s="12" t="inlineStr">
+        <is>
+          <t>LTC2 Français
 (TD - Salle 26)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V22" s="14" t="inlineStr">
-        <is>
-          <t>Electricité
+GC S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="V22" s="6" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
 (TD - Salle 27)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="W22" s="10" t="inlineStr">
-        <is>
-          <t>Algèbre 2
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
 (TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="X22" s="11" t="inlineStr">
+GB-GEG S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="X22" s="10" t="inlineStr">
+        <is>
+          <t>Bases de Données
+(TD - Salle 29)
+GB-GEG S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="Y22" s="15" t="inlineStr">
         <is>
           <t>Mécanique des Fluides et Transfert Thermique
-(TD - Salle 29)
-GP S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="Y22" s="13" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
 (TD - Salle 30)
-GP-GI S2 - Groupe: 4</t>
+GB-GEG S2 - Groupe: 5</t>
         </is>
       </c>
       <c r="Z22" s="7" t="n"/>
@@ -2351,26 +2345,26 @@
           <t>10:35</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Systèmes d'Information et Bases de Données
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Bases de Données
 (CM - Amphi 1)
-Section: GI S4</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Physiologie Animale et Végétale
-(CM - Amphi 3)
-Section: GB S4</t>
-        </is>
-      </c>
+Section: GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
+(CM - Amphi 2)
+Section: GP S4</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n"/>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Pétrographie et Minéralogie
+          <t>Structure de la matière
 (CM - Amphi 4)
-Section: GEG S4</t>
+Section: MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="F23" s="7" t="n"/>
@@ -2385,60 +2379,60 @@
       <c r="O23" s="7" t="n"/>
       <c r="P23" s="7" t="n"/>
       <c r="Q23" s="7" t="n"/>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>Analyse 2
+      <c r="R23" s="9" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
 (TD - Salle 23)
 GP-GI S2 - Groupe: 3</t>
         </is>
       </c>
-      <c r="S23" s="15" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
+      <c r="S23" s="9" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
 (TD - Salle 24)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="T23" s="10" t="inlineStr">
-        <is>
-          <t>LTC2 Français
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="T23" s="11" t="inlineStr">
+        <is>
+          <t>Pétrographie et Minéralogie
 (TD - Salle 25)
-GP S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="U23" s="13" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="U23" s="14" t="inlineStr">
+        <is>
+          <t>Développement Personnel
 (TD - Salle 26)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>Analyse de Données
+GC S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="V23" s="14" t="inlineStr">
+        <is>
+          <t>Recherche Opérationnelle
 (TD - Salle 27)
-GC S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="W23" s="11" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
+GI S4 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="W23" s="14" t="inlineStr">
+        <is>
+          <t>Structure des Données
 (TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="X23" s="12" t="inlineStr">
-        <is>
-          <t>Structure de la matière
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="X23" s="13" t="inlineStr">
+        <is>
+          <t>Systèmes d'Information et Bases de Données
 (TD - Salle 29)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="Y23" s="10" t="inlineStr">
-        <is>
-          <t>LTC2 Français
+MSD S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="Y23" s="8" t="inlineStr">
+        <is>
+          <t>Programmation Web
 (TD - Salle 30)
-GESE S4 - Groupe: 1</t>
+GI S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="Z23" s="7" t="n"/>
@@ -2453,13 +2447,7 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(CM - Amphi 1)
-Section: GI S4</t>
-        </is>
-      </c>
+      <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
@@ -2475,60 +2463,54 @@
       <c r="O24" s="7" t="n"/>
       <c r="P24" s="7" t="n"/>
       <c r="Q24" s="7" t="n"/>
-      <c r="R24" s="8" t="inlineStr">
+      <c r="R24" s="9" t="inlineStr">
         <is>
           <t>Langue Etrangère 2
 (TD - Salle 23)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="S24" s="9" t="inlineStr">
-        <is>
-          <t>Culture digitale
+MSD-GC-GESE S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="S24" s="12" t="inlineStr">
+        <is>
+          <t>Algèbre 2
 (TD - Salle 24)
-MSD-GC-GESE S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="T24" s="11" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
-(TD - Salle 25)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="U24" s="5" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="T24" s="7" t="n"/>
+      <c r="U24" s="11" t="inlineStr">
+        <is>
+          <t>Analyse 2
 (TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="V24" s="12" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 27)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 28)
 MSD-GC-GESE S2 - Groupe: 4</t>
         </is>
       </c>
-      <c r="V24" s="9" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 27)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
-(TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="X24" s="15" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
+      <c r="X24" s="11" t="inlineStr">
+        <is>
+          <t>Analyse 2
 (TD - Salle 29)
-GB-GEG S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="Y24" s="12" t="inlineStr">
-        <is>
-          <t>Structure de la matière
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="Y24" s="14" t="inlineStr">
+        <is>
+          <t>Structure des Données
 (TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 5</t>
+GI S4 - Groupe: 2</t>
         </is>
       </c>
       <c r="Z24" s="7" t="n"/>
@@ -2544,19 +2526,19 @@
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
-(CM - Amphi 2)
-Section: GB-GEG S2</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Géologie Structurale
+(CM - Amphi 3)
+Section: GEG S4</t>
+        </is>
+      </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Langue Etrangère 2
+          <t>Programmation Web
 (CM - Amphi 4)
-Section: MSD-GC-GESE S2</t>
+Section: GI S4</t>
         </is>
       </c>
       <c r="F25" s="7" t="n"/>
@@ -2571,60 +2553,60 @@
       <c r="O25" s="7" t="n"/>
       <c r="P25" s="7" t="n"/>
       <c r="Q25" s="7" t="n"/>
-      <c r="R25" s="14" t="inlineStr">
-        <is>
-          <t>Electricité
+      <c r="R25" s="9" t="inlineStr">
+        <is>
+          <t>Structure de la matière
 (TD - Salle 23)
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
+(TD - Salle 24)
+MSD-GC-GESE S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="T25" s="11" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
+(TD - Salle 25)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="U25" s="12" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 26)
+GP S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="V25" s="14" t="inlineStr">
+        <is>
+          <t>Métrologie Capteurs
+(TD - Salle 27)
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 28)
 GP-GI S2 - Groupe: 2</t>
         </is>
       </c>
-      <c r="S25" s="12" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 24)
+      <c r="X25" s="9" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 29)
 GP-GI S2 - Groupe: 5</t>
         </is>
       </c>
-      <c r="T25" s="11" t="inlineStr">
-        <is>
-          <t>Analyse 4
-(TD - Salle 25)
+      <c r="Y25" s="9" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
+(TD - Salle 30)
 MSD S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="U25" s="10" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 26)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="V25" s="9" t="inlineStr">
-        <is>
-          <t>Géomatique
-(TD - Salle 27)
-GEG S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="W25" s="9" t="inlineStr">
-        <is>
-          <t>Systèmes d'Information et Bases de Données
-(TD - Salle 28)
-GI S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="X25" s="5" t="inlineStr">
-        <is>
-          <t>Thermodynamique Chimique et Cinétique
-(TD - Salle 29)
-GC S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="Y25" s="8" t="inlineStr">
-        <is>
-          <t>Biologie Moléculaire et Génétique
-(TD - Salle 30)
-GB S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="Z25" s="7" t="n"/>
@@ -2639,27 +2621,9 @@
           <t>16:35</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(CM - Amphi 1)
-Section: MSD-GC-GESE S2</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>Electricité
-(CM - Amphi 2)
-Section: GP-GI S2</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Analyse de Données
-(CM - Amphi 3)
-Section: GB S4</t>
-        </is>
-      </c>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
@@ -2673,54 +2637,60 @@
       <c r="O26" s="7" t="n"/>
       <c r="P26" s="7" t="n"/>
       <c r="Q26" s="7" t="n"/>
-      <c r="R26" s="14" t="inlineStr">
-        <is>
-          <t>Electrotechnique
+      <c r="R26" s="12" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
 (TD - Salle 23)
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="S26" s="14" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 24)
 GESE S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="S26" s="6" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
-(TD - Salle 24)
+      <c r="T26" s="14" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 25)
+GI S4 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="U26" s="14" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 26)
 MSD S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="T26" s="9" t="inlineStr">
+      <c r="V26" s="9" t="inlineStr">
         <is>
           <t>Culture digitale
-(TD - Salle 25)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="U26" s="11" t="inlineStr">
-        <is>
-          <t>Chimie Organique 2
-(TD - Salle 26)
-GC S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V26" s="7" t="n"/>
-      <c r="W26" s="8" t="inlineStr">
+(TD - Salle 27)
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 28)
+MSD-GC-GESE S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="X26" s="14" t="inlineStr">
         <is>
           <t>Structure des Données
-(TD - Salle 28)
+(TD - Salle 29)
 GP S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="X26" s="9" t="inlineStr">
+      <c r="Y26" s="9" t="inlineStr">
         <is>
           <t>Culture digitale
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="Y26" s="10" t="inlineStr">
-        <is>
-          <t>LTC2 Français
 (TD - Salle 30)
-GI S4 - Groupe: 2</t>
+MSD-GC-GESE S2 - Groupe: 6</t>
         </is>
       </c>
       <c r="Z26" s="7" t="n"/>
@@ -2742,22 +2712,16 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>Chimie Organique 2
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Développement Personnel
 (CM - Amphi 1)
-Section: GC S4</t>
+Section: GI S4</t>
         </is>
       </c>
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="7" t="n"/>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>Electrotechnique
-(CM - Amphi 4)
-Section: GESE S4</t>
-        </is>
-      </c>
+      <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
       <c r="H28" s="7" t="n"/>
@@ -2770,60 +2734,60 @@
       <c r="O28" s="7" t="n"/>
       <c r="P28" s="7" t="n"/>
       <c r="Q28" s="7" t="n"/>
-      <c r="R28" s="10" t="inlineStr">
+      <c r="R28" s="12" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
+(TD - Salle 23)
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="S28" s="12" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 24)
+MSD-GC-GESE S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="T28" s="14" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 25)
+GB S4 - Groupe:</t>
+        </is>
+      </c>
+      <c r="U28" s="9" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="V28" s="6" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="W28" s="12" t="inlineStr">
         <is>
           <t>LTC2 Français
-(TD - Salle 23)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="S28" s="15" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
-(TD - Salle 24)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="T28" s="10" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="U28" s="9" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 26)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="V28" s="5" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(TD - Salle 27)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="W28" s="15" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
 (TD - Salle 28)
-GB-GEG S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="X28" s="15" t="inlineStr">
-        <is>
-          <t>Programmation Web
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="X28" s="12" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
 (TD - Salle 29)
-GI S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="Y28" s="12" t="inlineStr">
-        <is>
-          <t>Géologie Structurale
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="Y28" s="11" t="inlineStr">
+        <is>
+          <t>Analyse 2
 (TD - Salle 30)
-GEG S4 - Groupe: 1</t>
+MSD-GC-GESE S2 - Groupe: 3</t>
         </is>
       </c>
       <c r="Z28" s="7" t="n"/>
@@ -2838,20 +2802,26 @@
           <t>10:35</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Structure des Données
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Pétrographie et Minéralogie
 (CM - Amphi 1)
-Section: GI S4</t>
+Section: GEG S4</t>
         </is>
       </c>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Thermodynamique Chimique et Cinétique
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>Métrologie Capteurs
+(CM - Amphi 3)
+Section: GESE S4</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>Inférence Statistique et Applications
 (CM - Amphi 4)
-Section: GC S4</t>
+Section: MSD S4</t>
         </is>
       </c>
       <c r="F29" s="7" t="n"/>
@@ -2866,54 +2836,60 @@
       <c r="O29" s="7" t="n"/>
       <c r="P29" s="7" t="n"/>
       <c r="Q29" s="7" t="n"/>
-      <c r="R29" s="10" t="inlineStr">
-        <is>
-          <t>LTC2 Français
+      <c r="R29" s="8" t="inlineStr">
+        <is>
+          <t>Biologie Moléculaire et Génétique
 (TD - Salle 23)
-GEG S4 - Groupe: 1</t>
+GB S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="S29" s="9" t="inlineStr">
         <is>
-          <t>Culture digitale
+          <t>Structure de la matière
 (TD - Salle 24)
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="T29" s="10" t="inlineStr">
+        <is>
+          <t>Bases de Données
+(TD - Salle 25)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="U29" s="9" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 26)
 MSD-GC-GESE S2 - Groupe: 5</t>
         </is>
       </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 25)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="U29" s="9" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 26)
-GB-GEG S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="V29" s="14" t="inlineStr">
+      <c r="V29" s="5" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(TD - Salle 27)
+GB S4 - Groupe:</t>
+        </is>
+      </c>
+      <c r="W29" s="8" t="inlineStr">
         <is>
           <t>Electricité
-(TD - Salle 27)
+(TD - Salle 28)
 GP-GI S2 - Groupe: 3</t>
         </is>
       </c>
-      <c r="W29" s="7" t="n"/>
       <c r="X29" s="14" t="inlineStr">
         <is>
-          <t>Inférence Statistique et Applications
+          <t>Structure des Données
 (TD - Salle 29)
-MSD S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="Y29" s="13" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
+GI S4 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="Y29" s="9" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
 (TD - Salle 30)
-GP-GI S2 - Groupe: 2</t>
+GI S4 - Groupe: 2</t>
         </is>
       </c>
       <c r="Z29" s="7" t="n"/>
@@ -2928,20 +2904,20 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(CM - Amphi 1)
-Section: GP S4</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Recherche Opérationnelle
+(CM - Amphi 2)
+Section: GI S4</t>
+        </is>
+      </c>
       <c r="D30" s="7" t="n"/>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>Langue Etrangère 2
 (CM - Amphi 4)
-Section: GB-GEG S2</t>
+Section: MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="F30" s="7" t="n"/>
@@ -2956,54 +2932,42 @@
       <c r="O30" s="7" t="n"/>
       <c r="P30" s="7" t="n"/>
       <c r="Q30" s="7" t="n"/>
-      <c r="R30" s="14" t="inlineStr">
-        <is>
-          <t>Electricité
+      <c r="R30" s="12" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
 (TD - Salle 23)
-GP-GI S2 - Groupe: 4</t>
+GP-GI S2 - Groupe: 2</t>
         </is>
       </c>
       <c r="S30" s="9" t="inlineStr">
         <is>
-          <t>Culture digitale
+          <t>Analyse Numérique
 (TD - Salle 24)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="T30" s="7" t="n"/>
+      <c r="U30" s="9" t="inlineStr">
         <is>
           <t>Langue Etrangère 2
-(TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="U30" s="10" t="inlineStr">
-        <is>
-          <t>Algèbre 2
 (TD - Salle 26)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="V30" s="7" t="n"/>
-      <c r="W30" s="10" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="X30" s="12" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 29)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="Y30" s="6" t="inlineStr">
-        <is>
-          <t>Analyse 2
+GB-GEG S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="V30" s="6" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="W30" s="7" t="n"/>
+      <c r="X30" s="7" t="n"/>
+      <c r="Y30" s="8" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
 (TD - Salle 30)
-GP-GI S2 - Groupe: 5</t>
+GB-GEG S2 - Groupe: 5</t>
         </is>
       </c>
       <c r="Z30" s="7" t="n"/>
@@ -3018,28 +2982,28 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>LTC2 Français
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Analyse 4
 (CM - Amphi 1)
-Section: GB S4</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>Analyse 4
+Section: MSD S4</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
 (CM - Amphi 2)
-Section: GP S4</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="inlineStr">
-        <is>
-          <t>Programmation Web
-(CM - Amphi 3)
-Section: GI S4</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="n"/>
+Section: GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>Automatique
+(CM - Amphi 4)
+Section: GESE S4</t>
+        </is>
+      </c>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
       <c r="H31" s="7" t="n"/>
@@ -3052,54 +3016,60 @@
       <c r="O31" s="7" t="n"/>
       <c r="P31" s="7" t="n"/>
       <c r="Q31" s="7" t="n"/>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>Automatique
+      <c r="R31" s="9" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
 (TD - Salle 23)
-GESE S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="S31" s="11" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="S31" s="8" t="inlineStr">
+        <is>
+          <t>Programmation Web
 (TD - Salle 24)
-GB-GEG S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="T31" s="10" t="inlineStr">
-        <is>
-          <t>LTC2 Français
+GI S4 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="T31" s="9" t="inlineStr">
+        <is>
+          <t>Culture digitale
 (TD - Salle 25)
-MSD S4 - Groupe: 1</t>
+MSD-GC-GESE S2 - Groupe: 4</t>
         </is>
       </c>
       <c r="U31" s="5" t="inlineStr">
         <is>
+          <t>Analyse de Données
+(TD - Salle 26)
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="V31" s="9" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 27)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="W31" s="8" t="inlineStr">
+        <is>
+          <t>Electricité
+(TD - Salle 28)
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="X31" s="11" t="inlineStr">
+        <is>
           <t>Thermodynamique &amp; Mec. du Fluide
-(TD - Salle 26)
+(TD - Salle 29)
 MSD-GC-GESE S2 - Groupe: 3</t>
         </is>
       </c>
-      <c r="V31" s="14" t="inlineStr">
-        <is>
-          <t>Electricité
-(TD - Salle 27)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="W31" s="7" t="n"/>
-      <c r="X31" s="15" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="Y31" s="6" t="inlineStr">
-        <is>
-          <t>Analyse 2
+      <c r="Y31" s="9" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
 (TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 6</t>
+GI S4 - Groupe: 3</t>
         </is>
       </c>
       <c r="Z31" s="7" t="n"/>
@@ -3115,14 +3085,20 @@
         </is>
       </c>
       <c r="B32" s="7" t="n"/>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>Méthodes d'analyse
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
 (CM - Amphi 2)
-Section: GB S4</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="n"/>
+Section: GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Electrotechnique
+(CM - Amphi 3)
+Section: GESE S4</t>
+        </is>
+      </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -3136,60 +3112,60 @@
       <c r="O32" s="7" t="n"/>
       <c r="P32" s="7" t="n"/>
       <c r="Q32" s="7" t="n"/>
-      <c r="R32" s="9" t="inlineStr">
+      <c r="R32" s="12" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 23)
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
+(TD - Salle 24)
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="T32" s="9" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 25)
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="U32" s="14" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 26)
+GI S4 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="V32" s="9" t="inlineStr">
         <is>
           <t>Culture digitale
-(TD - Salle 23)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="S32" s="6" t="inlineStr">
-        <is>
-          <t>Optique Physique
-(TD - Salle 24)
-GP S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="T32" s="9" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 25)
-GB-GEG S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="U32" s="13" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
-(TD - Salle 26)
-GB-GEG S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="V32" s="6" t="inlineStr">
+(TD - Salle 27)
+MSD-GC-GESE S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="W32" s="13" t="inlineStr">
+        <is>
+          <t>Géologie Structurale
+(TD - Salle 28)
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="X32" s="11" t="inlineStr">
         <is>
           <t>Analyse 2
-(TD - Salle 27)
-GP-GI S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="W32" s="9" t="inlineStr">
-        <is>
-          <t>Systèmes d'Information et Bases de Données
-(TD - Salle 28)
-GI S4 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="X32" s="13" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
 (TD - Salle 29)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="Y32" s="5" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="Y32" s="11" t="inlineStr">
+        <is>
+          <t>Analyse 2
 (TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 6</t>
+GP-GI S2 - Groupe: 5</t>
         </is>
       </c>
       <c r="Z32" s="7" t="n"/>
@@ -3228,13 +3204,37 @@
       <c r="P34" s="7" t="n"/>
       <c r="Q34" s="7" t="n"/>
       <c r="R34" s="7" t="n"/>
-      <c r="S34" s="7" t="n"/>
-      <c r="T34" s="7" t="n"/>
+      <c r="S34" s="9" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 24)
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="T34" s="9" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 25)
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="U34" s="7" t="n"/>
       <c r="V34" s="7" t="n"/>
-      <c r="W34" s="7" t="n"/>
+      <c r="W34" s="9" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 28)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
       <c r="X34" s="7" t="n"/>
-      <c r="Y34" s="7" t="n"/>
+      <c r="Y34" s="6" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
+(TD - Salle 30)
+GB-GEG S2 - Groupe: 4</t>
+        </is>
+      </c>
       <c r="Z34" s="7" t="n"/>
       <c r="AA34" s="7" t="n"/>
       <c r="AB34" s="7" t="n"/>
@@ -3263,14 +3263,38 @@
       <c r="O35" s="7" t="n"/>
       <c r="P35" s="7" t="n"/>
       <c r="Q35" s="7" t="n"/>
-      <c r="R35" s="7" t="n"/>
+      <c r="R35" s="9" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 23)
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="S35" s="7" t="n"/>
       <c r="T35" s="7" t="n"/>
       <c r="U35" s="7" t="n"/>
-      <c r="V35" s="7" t="n"/>
+      <c r="V35" s="9" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 4</t>
+        </is>
+      </c>
       <c r="W35" s="7" t="n"/>
-      <c r="X35" s="7" t="n"/>
-      <c r="Y35" s="7" t="n"/>
+      <c r="X35" s="15" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
+(TD - Salle 29)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="Y35" s="8" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
+(TD - Salle 30)
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
       <c r="Z35" s="7" t="n"/>
       <c r="AA35" s="7" t="n"/>
       <c r="AB35" s="7" t="n"/>
@@ -3458,25 +3482,25 @@
           <t>LUNDI</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n"/>
-      <c r="C4" s="21" t="n"/>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="21" t="n"/>
-      <c r="F4" s="20" t="n"/>
-      <c r="G4" s="19" t="inlineStr">
-        <is>
-          <t>Inférence Statistique et Applications
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>Systèmes d'Information et Bases de Données
 (CM - Amphi 4)
 Section: MSD S4</t>
         </is>
       </c>
-      <c r="H4" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(TD - Salle 30)
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 23)
 MSD S4 - Groupe: 1</t>
         </is>
       </c>
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n"/>
@@ -3594,25 +3618,31 @@
           <t>MARDI</t>
         </is>
       </c>
-      <c r="B16" s="21" t="n"/>
-      <c r="C16" s="29" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(TD - Salle 27)
+MSD S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>Inférence Statistique et Applications
+(TD - Salle 30)
+MSD S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>LTC2 Français
 (CM - Amphi 2)
 Section: MSD S4</t>
         </is>
       </c>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="21" t="n"/>
       <c r="F16" s="20" t="n"/>
-      <c r="G16" s="21" t="n"/>
-      <c r="H16" s="28" t="inlineStr">
-        <is>
-          <t>Systèmes d'Information et Bases de Données
-(TD - Salle 28)
-MSD S4 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
@@ -3730,31 +3760,31 @@
           <t>MERCREDI</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
-        <is>
-          <t>Analyse de Données
-(TD - Salle 27)
-MSD S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
+(CM - Amphi 2)
+Section: MSD S4</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="18" t="inlineStr">
         <is>
           <t>Analyse de Données
 (CM - Amphi 3)
 Section: MSD S4</t>
         </is>
       </c>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="21" t="n"/>
-      <c r="F28" s="20" t="n"/>
-      <c r="G28" s="27" t="inlineStr">
+      <c r="H28" s="18" t="inlineStr">
         <is>
           <t>Analyse 4
-(CM - Amphi 2)
-Section: MSD S4</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="n"/>
+(TD - Salle 24)
+MSD S4 - Groupe: 1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n"/>
@@ -3872,34 +3902,28 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="21" t="n"/>
-      <c r="C40" s="28" t="inlineStr">
+      <c r="B40" s="25" t="n"/>
+      <c r="C40" s="23" t="inlineStr">
         <is>
           <t>Systèmes d'Information et Bases de Données
-(CM - Amphi 1)
-Section: MSD S4</t>
+(TD - Salle 29)
+MSD S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="D40" s="20" t="n"/>
-      <c r="E40" s="18" t="inlineStr">
+      <c r="E40" s="25" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="26" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
+(TD - Salle 30)
+MSD S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
         <is>
           <t>Développement Personnel
-(CM - Amphi 1)
-Section: MSD S4</t>
-        </is>
-      </c>
-      <c r="F40" s="20" t="n"/>
-      <c r="G40" s="27" t="inlineStr">
-        <is>
-          <t>Analyse 4
-(TD - Salle 25)
-MSD S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H40" s="29" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
-(TD - Salle 24)
+(TD - Salle 26)
 MSD S4 - Groupe: 1</t>
         </is>
       </c>
@@ -4020,31 +4044,31 @@
           <t>VENDREDI</t>
         </is>
       </c>
-      <c r="B52" s="21" t="n"/>
-      <c r="C52" s="19" t="inlineStr">
-        <is>
-          <t>Inférence Statistique et Applications
-(TD - Salle 29)
-MSD S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="D52" s="20" t="n"/>
-      <c r="E52" s="24" t="inlineStr">
-        <is>
-          <t>LTC2 Français
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>Développement Personnel
 (CM - Amphi 1)
 Section: MSD S4</t>
         </is>
       </c>
+      <c r="C52" s="27" t="inlineStr">
+        <is>
+          <t>Inférence Statistique et Applications
+(CM - Amphi 4)
+Section: MSD S4</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="25" t="n"/>
       <c r="F52" s="20" t="n"/>
-      <c r="G52" s="24" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(TD - Salle 25)
-MSD S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H52" s="21" t="n"/>
+      <c r="G52" s="18" t="inlineStr">
+        <is>
+          <t>Analyse 4
+(CM - Amphi 1)
+Section: MSD S4</t>
+        </is>
+      </c>
+      <c r="H52" s="25" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n"/>
@@ -4162,13 +4186,13 @@
           <t>SAMEDI</t>
         </is>
       </c>
-      <c r="B64" s="21" t="n"/>
-      <c r="C64" s="21" t="n"/>
+      <c r="B64" s="25" t="n"/>
+      <c r="C64" s="25" t="n"/>
       <c r="D64" s="20" t="n"/>
-      <c r="E64" s="21" t="n"/>
+      <c r="E64" s="25" t="n"/>
       <c r="F64" s="20" t="n"/>
-      <c r="G64" s="21" t="n"/>
-      <c r="H64" s="21" t="n"/>
+      <c r="G64" s="25" t="n"/>
+      <c r="H64" s="25" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
@@ -4395,41 +4419,41 @@
           <t>LUNDI</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 27)
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
+(CM - Amphi 2)
+Section: MSD-GC-GESE S2</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 24)
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="29" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 26)
 MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="C4" s="29" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="23" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(CM - Amphi 1)
-Section: MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="F4" s="20" t="n"/>
       <c r="G4" s="29" t="inlineStr">
         <is>
-          <t>Analyse 2
-(TD - Salle 27)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="H4" s="23" t="inlineStr">
+          <t>Thermodynamique &amp; Mec. du Fluide
+(CM - Amphi 2)
+Section: MSD-GC-GESE S2</t>
+        </is>
+      </c>
+      <c r="H4" s="26" t="inlineStr">
         <is>
           <t>Structure de la matière
-(TD - Salle 29)
-MSD-GC-GESE S2 - Groupe: 2</t>
+(TD - Salle 25)
+MSD-GC-GESE S2 - Groupe: 6</t>
         </is>
       </c>
     </row>
@@ -4461,29 +4485,29 @@
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
+      <c r="H7" s="26" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 28)
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n"/>
       <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 29)
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
-      <c r="G8" s="27" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
-(TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="H8" s="27" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
-(TD - Salle 24)
-MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n"/>
@@ -4497,19 +4521,19 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 29)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
+      <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 23)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -4524,24 +4548,18 @@
     <row r="12">
       <c r="A12" s="7" t="n"/>
       <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
+(TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 4</t>
+        </is>
+      </c>
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
-      <c r="G12" s="23" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 24)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H12" s="28" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 26)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
@@ -4551,7 +4569,13 @@
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
+      <c r="H13" s="29" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
+(TD - Salle 29)
+MSD-GC-GESE S2 - Groupe: 4</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -4579,43 +4603,31 @@
           <t>MARDI</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
-        <is>
-          <t>Analyse 2
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 23)
+MSD-GC-GESE S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>Algèbre 2
 (CM - Amphi 1)
 Section: MSD-GC-GESE S2</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 23)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
       <c r="D16" s="20" t="n"/>
-      <c r="E16" s="28" t="inlineStr">
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="26" t="inlineStr">
         <is>
           <t>Culture digitale
-(TD - Salle 29)
-MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="28" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(CM - Amphi 2)
+(CM - Amphi 4)
 Section: MSD-GC-GESE S2</t>
         </is>
       </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
-(CM - Amphi 1)
-Section: MSD-GC-GESE S2</t>
-        </is>
-      </c>
+      <c r="H16" s="25" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
@@ -4642,20 +4654,20 @@
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="7" t="n"/>
-      <c r="E19" s="27" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
-(TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n"/>
-      <c r="B20" s="7" t="n"/>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 25)
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
@@ -4676,21 +4688,9 @@
     <row r="22">
       <c r="A22" s="7" t="n"/>
       <c r="B22" s="7" t="n"/>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
-(TD - Salle 26)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="n"/>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
-(TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 2</t>
-        </is>
-      </c>
+      <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
@@ -4707,7 +4707,13 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
-      <c r="B24" s="7" t="n"/>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 24)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
@@ -4720,13 +4726,7 @@
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
-      <c r="E25" s="27" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
-(TD - Salle 24)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
@@ -4757,41 +4757,41 @@
           <t>MERCREDI</t>
         </is>
       </c>
-      <c r="B28" s="29" t="inlineStr">
-        <is>
-          <t>Analyse 2
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 28)
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
 (TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
+MSD-GC-GESE S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="29" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
 (TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="27" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
-(CM - Amphi 4)
-Section: MSD-GC-GESE S2</t>
+MSD-GC-GESE S2 - Groupe: 6</t>
         </is>
       </c>
       <c r="F28" s="20" t="n"/>
       <c r="G28" s="29" t="inlineStr">
         <is>
-          <t>Analyse 2
-(TD - Salle 27)
+          <t>Thermodynamique &amp; Mec. du Fluide
+(TD - Salle 29)
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="H28" s="28" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
+(TD - Salle 26)
 MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
-(TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 5</t>
         </is>
       </c>
     </row>
@@ -4807,7 +4807,13 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n"/>
-      <c r="B30" s="7" t="n"/>
+      <c r="B30" s="29" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
+(TD - Salle 29)
+MSD-GC-GESE S2 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="C30" s="7" t="n"/>
       <c r="D30" s="7" t="n"/>
       <c r="E30" s="7" t="n"/>
@@ -4827,19 +4833,31 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n"/>
-      <c r="B32" s="7" t="n"/>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 27)
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
-      <c r="G32" s="24" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 26)
-MSD-GC-GESE S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="n"/>
+      <c r="G32" s="26" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 28)
+MSD-GC-GESE S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="H32" s="29" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 29)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n"/>
@@ -4853,31 +4871,31 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n"/>
-      <c r="B34" s="23" t="inlineStr">
-        <is>
-          <t>Structure de la matière
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>Algèbre 2
 (TD - Salle 24)
-MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="C34" s="22" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 23)
+MSD-GC-GESE S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="C34" s="29" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 27)
 MSD-GC-GESE S2 - Groupe: 2</t>
         </is>
       </c>
       <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n"/>
+      <c r="E34" s="28" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
+(TD - Salle 24)
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="29" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 27)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
+      <c r="H34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n"/>
@@ -4891,19 +4909,31 @@
     </row>
     <row r="36">
       <c r="A36" s="7" t="n"/>
-      <c r="B36" s="7" t="n"/>
+      <c r="B36" s="26" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 25)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
-      <c r="G36" s="23" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 30)
+      <c r="G36" s="28" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
+(TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="H36" s="29" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 28)
 MSD-GC-GESE S2 - Groupe: 4</t>
         </is>
       </c>
-      <c r="H36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
@@ -4941,41 +4971,41 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="24" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="C40" s="27" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
-(TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="n"/>
-      <c r="E40" s="27" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
-(TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="F40" s="20" t="n"/>
-      <c r="G40" s="22" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
+      <c r="B40" s="29" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(CM - Amphi 1)
+Section: MSD-GC-GESE S2</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>Structure de la matière
 (CM - Amphi 4)
 Section: MSD-GC-GESE S2</t>
         </is>
       </c>
-      <c r="H40" s="24" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(CM - Amphi 1)
-Section: MSD-GC-GESE S2</t>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 23)
+MSD-GC-GESE S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="28" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
+(TD - Salle 24)
+MSD-GC-GESE S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="H40" s="26" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 30)
+MSD-GC-GESE S2 - Groupe: 6</t>
         </is>
       </c>
     </row>
@@ -4994,13 +5024,7 @@
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
       <c r="D42" s="7" t="n"/>
-      <c r="E42" s="23" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
       <c r="H42" s="7" t="n"/>
@@ -5010,29 +5034,23 @@
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="n"/>
-      <c r="E43" s="7" t="n"/>
+      <c r="E43" s="29" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n"/>
-      <c r="B44" s="22" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 23)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
       <c r="D44" s="7" t="n"/>
-      <c r="E44" s="18" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
-(TD - Salle 26)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
+      <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="7" t="n"/>
@@ -5052,16 +5070,28 @@
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
       <c r="D46" s="7" t="n"/>
-      <c r="E46" s="28" t="inlineStr">
-        <is>
-          <t>Culture digitale
+      <c r="E46" s="21" t="inlineStr">
+        <is>
+          <t>Algèbre 2
 (TD - Salle 24)
-MSD-GC-GESE S2 - Groupe: 2</t>
+MSD-GC-GESE S2 - Groupe: 3</t>
         </is>
       </c>
       <c r="F46" s="7" t="n"/>
-      <c r="G46" s="7" t="n"/>
-      <c r="H46" s="7" t="n"/>
+      <c r="G46" s="29" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
+(TD - Salle 25)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="H46" s="26" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 28)
+MSD-GC-GESE S2 - Groupe: 1</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n"/>
@@ -5075,22 +5105,10 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
-      <c r="B48" s="24" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="7" t="n"/>
-      <c r="E48" s="28" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 27)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
       <c r="H48" s="7" t="n"/>
@@ -5100,7 +5118,13 @@
       <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="7" t="n"/>
-      <c r="E49" s="7" t="n"/>
+      <c r="E49" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 28)
+MSD-GC-GESE S2 - Groupe: 4</t>
+        </is>
+      </c>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
       <c r="H49" s="7" t="n"/>
@@ -5131,41 +5155,41 @@
           <t>VENDREDI</t>
         </is>
       </c>
-      <c r="B52" s="24" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="C52" s="28" t="inlineStr">
+      <c r="B52" s="29" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 30)
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="C52" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(CM - Amphi 4)
+Section: MSD-GC-GESE S2</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="29" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
+(TD - Salle 29)
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="H52" s="26" t="inlineStr">
         <is>
           <t>Culture digitale
-(TD - Salle 24)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="D52" s="20" t="n"/>
-      <c r="E52" s="22" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="F52" s="20" t="n"/>
-      <c r="G52" s="18" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
-(TD - Salle 26)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="H52" s="18" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
-(TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 6</t>
+(TD - Salle 27)
+MSD-GC-GESE S2 - Groupe: 1</t>
         </is>
       </c>
     </row>
@@ -5201,16 +5225,16 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n"/>
-      <c r="B56" s="7" t="n"/>
+      <c r="B56" s="21" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 24)
+MSD-GC-GESE S2 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
-      <c r="E56" s="24" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 26)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
+      <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
@@ -5232,18 +5256,18 @@
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
-      <c r="G58" s="29" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 6</t>
+      <c r="G58" s="26" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 25)
+MSD-GC-GESE S2 - Groupe: 4</t>
         </is>
       </c>
       <c r="H58" s="28" t="inlineStr">
         <is>
-          <t>Culture digitale
-(TD - Salle 23)
-MSD-GC-GESE S2 - Groupe: 3</t>
+          <t>Mecanique du point / Optique
+(TD - Salle 24)
+MSD-GC-GESE S2 - Groupe: 2</t>
         </is>
       </c>
     </row>
@@ -5259,16 +5283,16 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n"/>
-      <c r="B60" s="7" t="n"/>
+      <c r="B60" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="n"/>
-      <c r="E60" s="24" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
       <c r="H60" s="7" t="n"/>
@@ -5309,13 +5333,13 @@
           <t>SAMEDI</t>
         </is>
       </c>
-      <c r="B64" s="21" t="n"/>
-      <c r="C64" s="21" t="n"/>
+      <c r="B64" s="25" t="n"/>
+      <c r="C64" s="25" t="n"/>
       <c r="D64" s="20" t="n"/>
-      <c r="E64" s="21" t="n"/>
+      <c r="E64" s="25" t="n"/>
       <c r="F64" s="20" t="n"/>
-      <c r="G64" s="21" t="n"/>
-      <c r="H64" s="21" t="n"/>
+      <c r="G64" s="25" t="n"/>
+      <c r="H64" s="25" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
@@ -5428,80 +5452,82 @@
       <c r="H75" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="73">
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="E52:E55"/>
-    <mergeCell ref="H4:H7"/>
+  <mergeCells count="75">
+    <mergeCell ref="B40:B51"/>
     <mergeCell ref="C34:C39"/>
     <mergeCell ref="A4:A15"/>
+    <mergeCell ref="G4:G15"/>
+    <mergeCell ref="H7:H9"/>
     <mergeCell ref="H16:H27"/>
+    <mergeCell ref="B56:B59"/>
+    <mergeCell ref="F28:F39"/>
     <mergeCell ref="F52:F63"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F28:F39"/>
-    <mergeCell ref="G8:G11"/>
     <mergeCell ref="B64:B75"/>
     <mergeCell ref="D64:D75"/>
+    <mergeCell ref="B4:B15"/>
     <mergeCell ref="G36:G39"/>
     <mergeCell ref="F64:F75"/>
     <mergeCell ref="A28:A39"/>
+    <mergeCell ref="G40:G45"/>
+    <mergeCell ref="H13:H15"/>
     <mergeCell ref="G16:G27"/>
-    <mergeCell ref="B16:B27"/>
     <mergeCell ref="G52:G57"/>
-    <mergeCell ref="E48:E51"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="G40:G51"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="B52:B55"/>
     <mergeCell ref="G28:G31"/>
+    <mergeCell ref="G46:G51"/>
     <mergeCell ref="A40:A51"/>
+    <mergeCell ref="E16:E27"/>
     <mergeCell ref="A52:A63"/>
-    <mergeCell ref="E60:E63"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="H34:H39"/>
     <mergeCell ref="H58:H63"/>
-    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E52:E63"/>
+    <mergeCell ref="E43:E45"/>
     <mergeCell ref="A64:A75"/>
     <mergeCell ref="C64:C75"/>
+    <mergeCell ref="C12:C15"/>
     <mergeCell ref="E64:E75"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="E34:E39"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="E28:E33"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="H36:H39"/>
     <mergeCell ref="F4:F15"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="B48:B51"/>
+    <mergeCell ref="H40:H45"/>
+    <mergeCell ref="H46:H51"/>
     <mergeCell ref="D40:D51"/>
+    <mergeCell ref="H32:H35"/>
     <mergeCell ref="F40:F51"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="H4:H6"/>
     <mergeCell ref="H52:H57"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B44:B47"/>
-    <mergeCell ref="B40:B43"/>
-    <mergeCell ref="C4:C15"/>
+    <mergeCell ref="B60:B63"/>
     <mergeCell ref="F16:F27"/>
     <mergeCell ref="E4:E15"/>
-    <mergeCell ref="B52:B63"/>
+    <mergeCell ref="C8:C11"/>
     <mergeCell ref="D52:D63"/>
-    <mergeCell ref="G4:G7"/>
-    <mergeCell ref="H12:H15"/>
-    <mergeCell ref="B34:B39"/>
-    <mergeCell ref="B10:B15"/>
-    <mergeCell ref="B28:B33"/>
+    <mergeCell ref="H10:H12"/>
     <mergeCell ref="H64:H75"/>
+    <mergeCell ref="C16:C27"/>
     <mergeCell ref="G58:G63"/>
-    <mergeCell ref="E28:E39"/>
-    <mergeCell ref="H40:H51"/>
-    <mergeCell ref="H28:H33"/>
+    <mergeCell ref="H28:H31"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B36:B39"/>
     <mergeCell ref="G32:G35"/>
     <mergeCell ref="A16:A27"/>
+    <mergeCell ref="B32:B33"/>
     <mergeCell ref="C40:C51"/>
-    <mergeCell ref="E56:E59"/>
+    <mergeCell ref="E49:E51"/>
     <mergeCell ref="D4:D15"/>
     <mergeCell ref="C52:C63"/>
-    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="B20:B23"/>
     <mergeCell ref="D16:D27"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="G12:G15"/>
     <mergeCell ref="G64:G75"/>
     <mergeCell ref="C28:C33"/>
     <mergeCell ref="D28:D39"/>
+    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="E40:E42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5568,27 +5594,39 @@
       </c>
       <c r="B4" s="18" t="inlineStr">
         <is>
-          <t>Développement Personnel
+          <t>Physiologie Animale et Végétale
 (CM - Amphi 1)
 Section: GB S4</t>
         </is>
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>Méthodes d'analyse
-(TD - Salle 25)
+          <t>Biochimie Métabolique et Enzymologie
+(CM - Amphi 3)
+Section: GB S4</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(CM - Amphi 2)
+Section: GB S4</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>Biochimie Métabolique et Enzymologie
+(TD - Salle 26)
 GB S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="21" t="n"/>
-      <c r="F4" s="20" t="n"/>
-      <c r="G4" s="21" t="n"/>
       <c r="H4" s="22" t="inlineStr">
         <is>
-          <t>Analyse de Données
-(TD - Salle 27)
-GB S4 - Groupe: 1</t>
+          <t>Biologie Moléculaire et Génétique
+(TD - Salle 24)
+Section: GB S4</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5687,13 @@
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>Physiologie Animale et Végétale
+(TD - Salle 23)
+Section: GB S4</t>
+        </is>
+      </c>
       <c r="H10" s="7" t="n"/>
     </row>
     <row r="11">
@@ -5708,22 +5752,40 @@
           <t>MARDI</t>
         </is>
       </c>
-      <c r="B16" s="21" t="n"/>
-      <c r="C16" s="21" t="n"/>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>Biologie Moléculaire et Génétique
+(CM - Amphi 4)
+Section: GB S4</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>Physiologie Animale et Végétale
+(TD - Salle 23)
+GB S4 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="D16" s="20" t="n"/>
-      <c r="E16" s="21" t="n"/>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 23)
+Section: GB S4</t>
+        </is>
+      </c>
       <c r="F16" s="20" t="n"/>
-      <c r="G16" s="22" t="inlineStr">
-        <is>
-          <t>Biologie Moléculaire et Génétique
-(CM - Amphi 3)
-Section: GB S4</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>Méthodes d'analyse
+(TD - Salle 29)
+GB S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
         <is>
           <t>Développement Personnel
-(TD - Salle 30)
+(TD - Salle 25)
 GB S4 - Groupe: 1</t>
         </is>
       </c>
@@ -5785,7 +5847,13 @@
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>Biochimie Métabolique et Enzymologie
+(TD - Salle 26)
+Section: GB S4</t>
+        </is>
+      </c>
       <c r="H22" s="7" t="n"/>
     </row>
     <row r="23">
@@ -5846,32 +5914,38 @@
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>Physiologie Animale et Végétale
-(TD - Salle 28)
+          <t>Méthodes d'analyse
+(CM - Amphi 1)
+Section: GB S4</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(CM - Amphi 3)
+Section: GB S4</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(CM - Amphi 1)
+Section: GB S4</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="18" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(TD - Salle 24)
 GB S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>LTC2 Français
-(TD - Salle 26)
-GB S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="21" t="n"/>
-      <c r="F28" s="20" t="n"/>
-      <c r="G28" s="25" t="inlineStr">
-        <is>
-          <t>Biochimie Métabolique et Enzymologie
-(CM - Amphi 4)
-Section: GB S4</t>
-        </is>
-      </c>
-      <c r="H28" s="25" t="inlineStr">
-        <is>
-          <t>Biochimie Métabolique et Enzymologie
-(TD - Salle 26)
+(TD - Salle 30)
 GB S4 - Groupe: 1</t>
         </is>
       </c>
@@ -5934,7 +6008,13 @@
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
+      <c r="H34" s="23" t="inlineStr">
+        <is>
+          <t>Méthodes d'analyse
+(TD - Salle 27)
+Section: GB S4</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n"/>
@@ -5992,31 +6072,13 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="21" t="n"/>
-      <c r="C40" s="23" t="inlineStr">
-        <is>
-          <t>Physiologie Animale et Végétale
-(CM - Amphi 3)
-Section: GB S4</t>
-        </is>
-      </c>
+      <c r="B40" s="25" t="n"/>
+      <c r="C40" s="25" t="n"/>
       <c r="D40" s="20" t="n"/>
-      <c r="E40" s="21" t="n"/>
+      <c r="E40" s="25" t="n"/>
       <c r="F40" s="20" t="n"/>
-      <c r="G40" s="22" t="inlineStr">
-        <is>
-          <t>Biologie Moléculaire et Génétique
-(TD - Salle 30)
-GB S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H40" s="22" t="inlineStr">
-        <is>
-          <t>Analyse de Données
-(CM - Amphi 3)
-Section: GB S4</t>
-        </is>
-      </c>
+      <c r="G40" s="25" t="n"/>
+      <c r="H40" s="25" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n"/>
@@ -6134,25 +6196,25 @@
           <t>VENDREDI</t>
         </is>
       </c>
-      <c r="B52" s="21" t="n"/>
-      <c r="C52" s="21" t="n"/>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 25)
+Section: GB S4</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
+          <t>Biologie Moléculaire et Génétique
+(TD - Salle 23)
+GB S4 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="D52" s="20" t="n"/>
-      <c r="E52" s="21" t="n"/>
+      <c r="E52" s="25" t="n"/>
       <c r="F52" s="20" t="n"/>
-      <c r="G52" s="24" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(CM - Amphi 1)
-Section: GB S4</t>
-        </is>
-      </c>
-      <c r="H52" s="19" t="inlineStr">
-        <is>
-          <t>Méthodes d'analyse
-(CM - Amphi 2)
-Section: GB S4</t>
-        </is>
-      </c>
+      <c r="G52" s="25" t="n"/>
+      <c r="H52" s="25" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n"/>
@@ -6207,7 +6269,13 @@
     <row r="58">
       <c r="A58" s="7" t="n"/>
       <c r="B58" s="7" t="n"/>
-      <c r="C58" s="7" t="n"/>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(TD - Salle 27)
+Section: GB S4</t>
+        </is>
+      </c>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
@@ -6270,13 +6338,13 @@
           <t>SAMEDI</t>
         </is>
       </c>
-      <c r="B64" s="21" t="n"/>
-      <c r="C64" s="21" t="n"/>
+      <c r="B64" s="25" t="n"/>
+      <c r="C64" s="25" t="n"/>
       <c r="D64" s="20" t="n"/>
-      <c r="E64" s="21" t="n"/>
+      <c r="E64" s="25" t="n"/>
       <c r="F64" s="20" t="n"/>
-      <c r="G64" s="21" t="n"/>
-      <c r="H64" s="21" t="n"/>
+      <c r="G64" s="25" t="n"/>
+      <c r="H64" s="25" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
@@ -6389,32 +6457,32 @@
       <c r="H75" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="53">
     <mergeCell ref="B40:B51"/>
     <mergeCell ref="A4:A15"/>
-    <mergeCell ref="G4:G15"/>
     <mergeCell ref="H16:H27"/>
     <mergeCell ref="F52:F63"/>
     <mergeCell ref="F28:F39"/>
     <mergeCell ref="B64:B75"/>
-    <mergeCell ref="H28:H39"/>
     <mergeCell ref="D64:D75"/>
     <mergeCell ref="B4:B15"/>
     <mergeCell ref="F64:F75"/>
+    <mergeCell ref="C58:C63"/>
     <mergeCell ref="A28:A39"/>
-    <mergeCell ref="G16:G27"/>
     <mergeCell ref="C28:C39"/>
     <mergeCell ref="B16:B27"/>
     <mergeCell ref="G40:G51"/>
     <mergeCell ref="A40:A51"/>
     <mergeCell ref="E16:E27"/>
     <mergeCell ref="A52:A63"/>
+    <mergeCell ref="H34:H39"/>
     <mergeCell ref="E52:E63"/>
     <mergeCell ref="H4:H15"/>
     <mergeCell ref="G52:G63"/>
     <mergeCell ref="A64:A75"/>
     <mergeCell ref="C64:C75"/>
     <mergeCell ref="E64:E75"/>
+    <mergeCell ref="G10:G15"/>
     <mergeCell ref="F4:F15"/>
     <mergeCell ref="D40:D51"/>
     <mergeCell ref="F40:F51"/>
@@ -6429,16 +6497,20 @@
     <mergeCell ref="E28:E39"/>
     <mergeCell ref="G28:G39"/>
     <mergeCell ref="H40:H51"/>
+    <mergeCell ref="H28:H33"/>
+    <mergeCell ref="C52:C57"/>
     <mergeCell ref="H52:H63"/>
     <mergeCell ref="A16:A27"/>
     <mergeCell ref="C40:C51"/>
+    <mergeCell ref="G4:G9"/>
     <mergeCell ref="E40:E51"/>
     <mergeCell ref="D4:D15"/>
-    <mergeCell ref="C52:C63"/>
     <mergeCell ref="D16:D27"/>
     <mergeCell ref="G64:G75"/>
+    <mergeCell ref="G16:G21"/>
     <mergeCell ref="B28:B39"/>
     <mergeCell ref="D28:D39"/>
+    <mergeCell ref="G22:G27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6503,40 +6575,40 @@
           <t>LUNDI</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
-(TD - Salle 30)
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>Bases de Données
+(TD - Salle 25)
 GB-GEG S2 - Groupe: 2</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>Bases de Données
+(TD - Salle 28)
+GB-GEG S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>Bases de Données
+(TD - Salle 25)
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(CM - Amphi 4)
+Section: GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
         <is>
           <t>Réactivité Chimique
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="27" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
-(TD - Salle 28)
-GB-GEG S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="n"/>
-      <c r="G4" s="25" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
-(TD - Salle 26)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="H4" s="25" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
-(CM - Amphi 4)
+(CM - Amphi 2)
 Section: GB-GEG S2</t>
         </is>
       </c>
@@ -6576,11 +6648,11 @@
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
       <c r="D8" s="7" t="n"/>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(TD - Salle 23)
-GB-GEG S2 - Groupe: 6</t>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 28)
+GB-GEG S2 - Groupe: 2</t>
         </is>
       </c>
       <c r="F8" s="7" t="n"/>
@@ -6599,30 +6671,24 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
-      <c r="B10" s="27" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
-(TD - Salle 28)
-GB-GEG S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Langue Etrangère 2
 (TD - Salle 24)
 GB-GEG S2 - Groupe: 4</t>
         </is>
       </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
+(TD - Salle 23)
+GB-GEG S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
-      <c r="G10" s="22" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 25)
-GB-GEG S2 - Groupe: 3</t>
-        </is>
-      </c>
+      <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="n"/>
     </row>
     <row r="11">
@@ -6640,11 +6706,11 @@
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="n"/>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>Réactivité Chimique
-(TD - Salle 24)
-GB-GEG S2 - Groupe: 3</t>
+(TD - Salle 30)
+GB-GEG S2 - Groupe: 1</t>
         </is>
       </c>
       <c r="F12" s="7" t="n"/>
@@ -6690,38 +6756,38 @@
       <c r="B16" s="27" t="inlineStr">
         <is>
           <t>Mécanique des Fluides et Transfert Thermique
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="C16" s="25" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
-(TD - Salle 30)
-GB-GEG S2 - Groupe: 3</t>
+(TD - Salle 28)
+GB-GEG S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 26)
+GB-GEG S2 - Groupe: 2</t>
         </is>
       </c>
       <c r="D16" s="20" t="n"/>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>Bases de Données
+(TD - Salle 25)
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="27" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
+(TD - Salle 25)
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="H16" s="27" t="inlineStr">
         <is>
           <t>Géodynamique externe
-(CM - Amphi 2)
-Section: GB-GEG S2</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="26" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
-(TD - Salle 24)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H16" s="25" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
 (TD - Salle 26)
-GB-GEG S2 - Groupe: 5</t>
+GB-GEG S2 - Groupe: 6</t>
         </is>
       </c>
     </row>
@@ -6750,7 +6816,13 @@
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 26)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
@@ -6758,13 +6830,7 @@
     <row r="20">
       <c r="A20" s="7" t="n"/>
       <c r="B20" s="7" t="n"/>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 2</t>
-        </is>
-      </c>
+      <c r="C20" s="7" t="n"/>
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
@@ -6783,29 +6849,41 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n"/>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(TD - Salle 23)
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
+(TD - Salle 30)
 GB-GEG S2 - Groupe: 4</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n"/>
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
+(TD - Salle 25)
+GB-GEG S2 - Groupe: 4</t>
+        </is>
+      </c>
       <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
+      <c r="E22" s="27" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
+(TD - Salle 24)
+GB-GEG S2 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="F22" s="7" t="n"/>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>Bases de Données
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
+(TD - Salle 28)
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="H22" s="27" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
 (TD - Salle 29)
 GB-GEG S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="H22" s="26" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 6</t>
         </is>
       </c>
     </row>
@@ -6822,13 +6900,7 @@
     <row r="24">
       <c r="A24" s="7" t="n"/>
       <c r="B24" s="7" t="n"/>
-      <c r="C24" s="22" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 27)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
@@ -6840,7 +6912,13 @@
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
+      <c r="E25" s="27" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
+(TD - Salle 28)
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
@@ -6871,41 +6949,41 @@
           <t>MERCREDI</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(CM - Amphi 1)
-Section: GB-GEG S2</t>
+      <c r="B28" s="28" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
+(TD - Salle 30)
+GB-GEG S2 - Groupe: 1</t>
         </is>
       </c>
       <c r="C28" s="27" t="inlineStr">
         <is>
           <t>Mécanique des Fluides et Transfert Thermique
-(CM - Amphi 1)
-Section: GB-GEG S2</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="22" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 23)
-GB-GEG S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="F28" s="20" t="n"/>
-      <c r="G28" s="28" t="inlineStr">
-        <is>
-          <t>Culture digitale
 (TD - Salle 25)
 GB-GEG S2 - Groupe: 1</t>
         </is>
       </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 5</t>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="28" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
+(TD - Salle 30)
+GB-GEG S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="27" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
+(CM - Amphi 2)
+Section: GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="H28" s="26" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(CM - Amphi 4)
+Section: GB-GEG S2</t>
         </is>
       </c>
     </row>
@@ -6934,13 +7012,7 @@
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="n"/>
-      <c r="E31" s="22" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 24)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
       <c r="H31" s="7" t="n"/>
@@ -6953,13 +7025,7 @@
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
-      <c r="H32" s="26" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
-(TD - Salle 24)
-GB-GEG S2 - Groupe: 4</t>
-        </is>
-      </c>
+      <c r="H32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n"/>
@@ -6978,9 +7044,9 @@
       <c r="D34" s="7" t="n"/>
       <c r="E34" s="26" t="inlineStr">
         <is>
-          <t>Géodynamique externe
-(TD - Salle 28)
-GB-GEG S2 - Groupe: 3</t>
+          <t>Culture digitale
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 1</t>
         </is>
       </c>
       <c r="F34" s="7" t="n"/>
@@ -7005,26 +7071,14 @@
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
-      <c r="H36" s="26" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
-(TD - Salle 28)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="H36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="n"/>
-      <c r="E37" s="27" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
       <c r="H37" s="7" t="n"/>
@@ -7055,43 +7109,25 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="28" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(CM - Amphi 2)
-Section: GB-GEG S2</t>
-        </is>
-      </c>
-      <c r="C40" s="25" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
-(TD - Salle 26)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="n"/>
-      <c r="E40" s="22" t="inlineStr">
+      <c r="B40" s="26" t="inlineStr">
         <is>
           <t>Langue Etrangère 2
 (TD - Salle 23)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="inlineStr">
+        <is>
+          <t>Bases de Données
+(CM - Amphi 1)
+Section: GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="25" t="n"/>
       <c r="F40" s="20" t="n"/>
-      <c r="G40" s="26" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
-(CM - Amphi 2)
-Section: GB-GEG S2</t>
-        </is>
-      </c>
-      <c r="H40" s="28" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 4</t>
-        </is>
-      </c>
+      <c r="G40" s="25" t="n"/>
+      <c r="H40" s="25" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n"/>
@@ -7105,7 +7141,13 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n"/>
-      <c r="B42" s="7" t="n"/>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>Bases de Données
+(TD - Salle 29)
+GB-GEG S2 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="C42" s="7" t="n"/>
       <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
@@ -7125,16 +7167,16 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n"/>
-      <c r="B44" s="7" t="n"/>
+      <c r="B44" s="28" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="C44" s="7" t="n"/>
       <c r="D44" s="7" t="n"/>
-      <c r="E44" s="26" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 2</t>
-        </is>
-      </c>
+      <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="7" t="n"/>
@@ -7151,25 +7193,19 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n"/>
-      <c r="B46" s="7" t="n"/>
-      <c r="C46" s="26" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
-(TD - Salle 24)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
+(TD - Salle 25)
+GB-GEG S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="n"/>
       <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
-      <c r="H46" s="28" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 25)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="H46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n"/>
@@ -7183,16 +7219,16 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
-      <c r="B48" s="7" t="n"/>
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
+(TD - Salle 30)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="7" t="n"/>
-      <c r="E48" s="27" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
-(TD - Salle 25)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
       <c r="H48" s="7" t="n"/>
@@ -7209,7 +7245,13 @@
     </row>
     <row r="50">
       <c r="A50" s="7" t="n"/>
-      <c r="B50" s="7" t="n"/>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
+(TD - Salle 28)
+GB-GEG S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
@@ -7233,41 +7275,41 @@
           <t>VENDREDI</t>
         </is>
       </c>
-      <c r="B52" s="26" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
-(TD - Salle 28)
-GB-GEG S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="C52" s="28" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 26)
-GB-GEG S2 - Groupe: 3</t>
+      <c r="B52" s="28" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="C52" s="19" t="inlineStr">
+        <is>
+          <t>Bases de Données
+(TD - Salle 25)
+GB-GEG S2 - Groupe: 5</t>
         </is>
       </c>
       <c r="D52" s="20" t="n"/>
-      <c r="E52" s="22" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(CM - Amphi 4)
+      <c r="E52" s="28" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="27" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
+(CM - Amphi 2)
 Section: GB-GEG S2</t>
         </is>
       </c>
-      <c r="F52" s="20" t="n"/>
-      <c r="G52" s="26" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="H52" s="25" t="inlineStr">
+      <c r="H52" s="28" t="inlineStr">
         <is>
           <t>Biologie Animale et Végétale
-(TD - Salle 26)
-GB-GEG S2 - Groupe: 4</t>
+(CM - Amphi 2)
+Section: GB-GEG S2</t>
         </is>
       </c>
     </row>
@@ -7293,13 +7335,7 @@
     </row>
     <row r="55">
       <c r="A55" s="7" t="n"/>
-      <c r="B55" s="26" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
-(TD - Salle 24)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
@@ -7312,7 +7348,13 @@
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
-      <c r="E56" s="7" t="n"/>
+      <c r="E56" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 26)
+GB-GEG S2 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
@@ -7329,31 +7371,13 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n"/>
-      <c r="B58" s="18" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(TD - Salle 27)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
-      <c r="G58" s="27" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
-(TD - Salle 24)
-GB-GEG S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="H58" s="28" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 25)
-GB-GEG S2 - Groupe: 2</t>
-        </is>
-      </c>
+      <c r="G58" s="7" t="n"/>
+      <c r="H58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n"/>
@@ -7370,20 +7394,20 @@
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="n"/>
-      <c r="E60" s="7" t="n"/>
+      <c r="E60" s="22" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
+(TD - Salle 30)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
       <c r="H60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n"/>
-      <c r="B61" s="28" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 26)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
@@ -7417,13 +7441,25 @@
           <t>SAMEDI</t>
         </is>
       </c>
-      <c r="B64" s="21" t="n"/>
-      <c r="C64" s="21" t="n"/>
+      <c r="B64" s="26" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 24)
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="C64" s="22" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
+(TD - Salle 30)
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
       <c r="D64" s="20" t="n"/>
-      <c r="E64" s="21" t="n"/>
+      <c r="E64" s="25" t="n"/>
       <c r="F64" s="20" t="n"/>
-      <c r="G64" s="21" t="n"/>
-      <c r="H64" s="21" t="n"/>
+      <c r="G64" s="25" t="n"/>
+      <c r="H64" s="25" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
@@ -7447,8 +7483,20 @@
     </row>
     <row r="67">
       <c r="A67" s="7" t="n"/>
-      <c r="B67" s="7" t="n"/>
-      <c r="C67" s="7" t="n"/>
+      <c r="B67" s="28" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
+(TD - Salle 30)
+GB-GEG S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="C67" s="26" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 4</t>
+        </is>
+      </c>
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
@@ -7477,8 +7525,20 @@
     </row>
     <row r="70">
       <c r="A70" s="7" t="n"/>
-      <c r="B70" s="7" t="n"/>
-      <c r="C70" s="7" t="n"/>
+      <c r="B70" s="26" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 25)
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="C70" s="27" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
+(TD - Salle 29)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
@@ -7507,8 +7567,20 @@
     </row>
     <row r="73">
       <c r="A73" s="7" t="n"/>
-      <c r="B73" s="7" t="n"/>
-      <c r="C73" s="7" t="n"/>
+      <c r="B73" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 28)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="C73" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 23)
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
@@ -7536,79 +7608,80 @@
       <c r="H75" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="73">
+  <mergeCells count="74">
     <mergeCell ref="B4:B9"/>
-    <mergeCell ref="B40:B51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="E52:E55"/>
+    <mergeCell ref="C67:C69"/>
     <mergeCell ref="B22:B27"/>
+    <mergeCell ref="C70:C72"/>
     <mergeCell ref="A4:A15"/>
+    <mergeCell ref="G4:G15"/>
     <mergeCell ref="E8:E11"/>
     <mergeCell ref="F52:F63"/>
     <mergeCell ref="F28:F39"/>
-    <mergeCell ref="B64:B75"/>
-    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="H28:H39"/>
     <mergeCell ref="B16:B21"/>
+    <mergeCell ref="B46:B47"/>
     <mergeCell ref="D64:D75"/>
     <mergeCell ref="F64:F75"/>
-    <mergeCell ref="B55:B57"/>
     <mergeCell ref="A28:A39"/>
+    <mergeCell ref="B42:B43"/>
     <mergeCell ref="C28:C39"/>
-    <mergeCell ref="G52:G57"/>
-    <mergeCell ref="E48:E51"/>
     <mergeCell ref="G40:G51"/>
+    <mergeCell ref="E22:E24"/>
     <mergeCell ref="E4:E7"/>
     <mergeCell ref="C4:C9"/>
-    <mergeCell ref="E16:E27"/>
     <mergeCell ref="A40:A51"/>
-    <mergeCell ref="E44:E47"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="E25:E27"/>
     <mergeCell ref="A52:A63"/>
-    <mergeCell ref="H58:H63"/>
-    <mergeCell ref="E52:E63"/>
+    <mergeCell ref="E60:E63"/>
+    <mergeCell ref="E16:E18"/>
     <mergeCell ref="H4:H15"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="G52:G63"/>
     <mergeCell ref="A64:A75"/>
-    <mergeCell ref="C16:C19"/>
-    <mergeCell ref="C64:C75"/>
     <mergeCell ref="C10:C15"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="E34:E39"/>
     <mergeCell ref="E64:E75"/>
-    <mergeCell ref="H36:H39"/>
-    <mergeCell ref="E37:E39"/>
-    <mergeCell ref="H46:H51"/>
-    <mergeCell ref="G10:G15"/>
+    <mergeCell ref="E28:E33"/>
     <mergeCell ref="F4:F15"/>
-    <mergeCell ref="H40:H45"/>
+    <mergeCell ref="C22:C27"/>
     <mergeCell ref="D40:D51"/>
-    <mergeCell ref="H32:H35"/>
-    <mergeCell ref="C46:C51"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="F40:F51"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E40:E43"/>
-    <mergeCell ref="F40:F51"/>
-    <mergeCell ref="H52:H57"/>
     <mergeCell ref="F16:F27"/>
+    <mergeCell ref="B52:B63"/>
     <mergeCell ref="H22:H27"/>
     <mergeCell ref="D52:D63"/>
-    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="C73:C75"/>
     <mergeCell ref="H64:H75"/>
     <mergeCell ref="B10:B15"/>
     <mergeCell ref="H16:H21"/>
-    <mergeCell ref="C40:C45"/>
-    <mergeCell ref="G58:G63"/>
-    <mergeCell ref="H28:H31"/>
+    <mergeCell ref="B40:B41"/>
     <mergeCell ref="G28:G39"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="H40:H51"/>
+    <mergeCell ref="B70:B72"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="H52:H63"/>
     <mergeCell ref="A16:A27"/>
-    <mergeCell ref="G4:G9"/>
+    <mergeCell ref="C40:C51"/>
+    <mergeCell ref="E40:E51"/>
+    <mergeCell ref="E56:E59"/>
     <mergeCell ref="D4:D15"/>
-    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="B73:B75"/>
     <mergeCell ref="C52:C63"/>
     <mergeCell ref="E12:E15"/>
     <mergeCell ref="D16:D27"/>
+    <mergeCell ref="E19:E21"/>
     <mergeCell ref="G64:G75"/>
     <mergeCell ref="G16:G21"/>
     <mergeCell ref="B28:B39"/>
     <mergeCell ref="D28:D39"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="C24:C27"/>
     <mergeCell ref="G22:G27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7674,22 +7747,28 @@
           <t>LUNDI</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n"/>
-      <c r="C4" s="21" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>Éléments de Génie Chimique
+(TD - Salle 30)
+GC S4 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="D4" s="20" t="n"/>
-      <c r="E4" s="21" t="n"/>
+      <c r="E4" s="25" t="n"/>
       <c r="F4" s="20" t="n"/>
-      <c r="G4" s="24" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>Chimie Minérale 2
-(CM - Amphi 3)
-Section: GC S4</t>
-        </is>
-      </c>
-      <c r="H4" s="24" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(TD - Salle 25)
+(TD - Salle 24)
+GC S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(TD - Salle 26)
 GC S4 - Groupe: 1</t>
         </is>
       </c>
@@ -7810,31 +7889,37 @@
           <t>MARDI</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>Thermodynamique Chimique et Cinétique
+(TD - Salle 29)
+GC S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="n"/>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(CM - Amphi 2)
+Section: GC S4</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="19" t="inlineStr">
+        <is>
+          <t>Chimie Organique 2
 (TD - Salle 30)
 GC S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
-        <is>
-          <t>Éléments de Génie Chimique
-(CM - Amphi 3)
+      <c r="H16" s="19" t="inlineStr">
+        <is>
+          <t>Chimie Minérale 2
+(CM - Amphi 1)
 Section: GC S4</t>
         </is>
       </c>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="21" t="n"/>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="24" t="inlineStr">
-        <is>
-          <t>Chimie Minérale 2
-(TD - Salle 26)
-GC S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
@@ -7952,22 +8037,34 @@
           <t>MERCREDI</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n"/>
-      <c r="C28" s="21" t="n"/>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="21" t="n"/>
-      <c r="F28" s="20" t="n"/>
-      <c r="G28" s="25" t="inlineStr">
-        <is>
-          <t>Éléments de Génie Chimique
-(TD - Salle 24)
-GC S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H28" s="22" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>Analyse de Données
 (CM - Amphi 3)
+Section: GC S4</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>Éléments de Génie Chimique
+(CM - Amphi 1)
+Section: GC S4</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="19" t="inlineStr">
+        <is>
+          <t>Chimie Organique 2
+(CM - Amphi 4)
+Section: GC S4</t>
+        </is>
+      </c>
+      <c r="H28" s="29" t="inlineStr">
+        <is>
+          <t>Thermodynamique Chimique et Cinétique
+(CM - Amphi 1)
 Section: GC S4</t>
         </is>
       </c>
@@ -8088,37 +8185,25 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="21" t="n"/>
-      <c r="C40" s="22" t="inlineStr">
-        <is>
-          <t>Analyse de Données
-(TD - Salle 27)
-GC S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="n"/>
-      <c r="E40" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(CM - Amphi 1)
-Section: GC S4</t>
-        </is>
-      </c>
-      <c r="F40" s="20" t="n"/>
-      <c r="G40" s="18" t="inlineStr">
-        <is>
-          <t>Thermodynamique Chimique et Cinétique
-(TD - Salle 29)
-GC S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H40" s="27" t="inlineStr">
-        <is>
-          <t>Chimie Organique 2
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>LTC2 Français
 (TD - Salle 26)
 GC S4 - Groupe: 1</t>
         </is>
       </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 26)
+GC S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="25" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="25" t="n"/>
+      <c r="H40" s="25" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n"/>
@@ -8236,31 +8321,19 @@
           <t>VENDREDI</t>
         </is>
       </c>
-      <c r="B52" s="27" t="inlineStr">
-        <is>
-          <t>Chimie Organique 2
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>Développement Personnel
 (CM - Amphi 1)
 Section: GC S4</t>
         </is>
       </c>
-      <c r="C52" s="18" t="inlineStr">
-        <is>
-          <t>Thermodynamique Chimique et Cinétique
-(CM - Amphi 4)
-Section: GC S4</t>
-        </is>
-      </c>
+      <c r="C52" s="25" t="n"/>
       <c r="D52" s="20" t="n"/>
-      <c r="E52" s="24" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(CM - Amphi 1)
-Section: GC S4</t>
-        </is>
-      </c>
+      <c r="E52" s="25" t="n"/>
       <c r="F52" s="20" t="n"/>
-      <c r="G52" s="21" t="n"/>
-      <c r="H52" s="21" t="n"/>
+      <c r="G52" s="25" t="n"/>
+      <c r="H52" s="25" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n"/>
@@ -8378,13 +8451,13 @@
           <t>SAMEDI</t>
         </is>
       </c>
-      <c r="B64" s="21" t="n"/>
-      <c r="C64" s="21" t="n"/>
+      <c r="B64" s="25" t="n"/>
+      <c r="C64" s="25" t="n"/>
       <c r="D64" s="20" t="n"/>
-      <c r="E64" s="21" t="n"/>
+      <c r="E64" s="25" t="n"/>
       <c r="F64" s="20" t="n"/>
-      <c r="G64" s="21" t="n"/>
-      <c r="H64" s="21" t="n"/>
+      <c r="G64" s="25" t="n"/>
+      <c r="H64" s="25" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
@@ -8611,25 +8684,31 @@
           <t>LUNDI</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(CM - Amphi 1)
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(CM - Amphi 2)
 Section: GEG S4</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
-        <is>
-          <t>Analyse de Données
-(TD - Salle 27)
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t>Méthodes d'analyse
+(TD - Salle 30)
 GEG S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="21" t="n"/>
-      <c r="F4" s="20" t="n"/>
-      <c r="G4" s="21" t="n"/>
-      <c r="H4" s="21" t="n"/>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Géomatique
+(TD - Salle 30)
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n"/>
@@ -8747,31 +8826,25 @@
           <t>MARDI</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>Géologie Structurale
-(CM - Amphi 3)
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 26)
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>Géomatique
+(CM - Amphi 2)
 Section: GEG S4</t>
         </is>
       </c>
-      <c r="C16" s="28" t="inlineStr">
-        <is>
-          <t>Pétrographie et Minéralogie
-(TD - Salle 25)
-GEG S4 - Groupe: 1</t>
-        </is>
-      </c>
       <c r="D16" s="20" t="n"/>
-      <c r="E16" s="21" t="n"/>
+      <c r="E16" s="25" t="n"/>
       <c r="F16" s="20" t="n"/>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(TD - Salle 30)
-GEG S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
@@ -8889,25 +8962,31 @@
           <t>MERCREDI</t>
         </is>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>Méthodes d'analyse
-(TD - Salle 29)
-GEG S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="n"/>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="21" t="n"/>
-      <c r="F28" s="20" t="n"/>
-      <c r="G28" s="28" t="inlineStr">
-        <is>
-          <t>Géomatique
+(CM - Amphi 1)
+Section: GEG S4</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>Analyse de Données
 (CM - Amphi 3)
 Section: GEG S4</t>
         </is>
       </c>
-      <c r="H28" s="21" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(CM - Amphi 1)
+Section: GEG S4</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="25" t="n"/>
+      <c r="H28" s="25" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n"/>
@@ -9025,31 +9104,25 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="21" t="n"/>
-      <c r="C40" s="28" t="inlineStr">
+      <c r="B40" s="25" t="n"/>
+      <c r="C40" s="29" t="inlineStr">
         <is>
           <t>Pétrographie et Minéralogie
-(CM - Amphi 4)
-Section: GEG S4</t>
+(TD - Salle 25)
+GEG S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="D40" s="20" t="n"/>
-      <c r="E40" s="21" t="n"/>
+      <c r="E40" s="25" t="n"/>
       <c r="F40" s="20" t="n"/>
-      <c r="G40" s="28" t="inlineStr">
-        <is>
-          <t>Géomatique
-(TD - Salle 27)
-GEG S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H40" s="22" t="inlineStr">
-        <is>
-          <t>Analyse de Données
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>Géologie Structurale
 (CM - Amphi 3)
 Section: GEG S4</t>
         </is>
       </c>
+      <c r="H40" s="25" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n"/>
@@ -9167,35 +9240,35 @@
           <t>VENDREDI</t>
         </is>
       </c>
-      <c r="B52" s="23" t="inlineStr">
-        <is>
-          <t>Géologie Structurale
-(TD - Salle 30)
+      <c r="B52" s="21" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 28)
 GEG S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="C52" s="24" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(TD - Salle 23)
-GEG S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="D52" s="20" t="n"/>
-      <c r="E52" s="21" t="n"/>
-      <c r="F52" s="20" t="n"/>
-      <c r="G52" s="24" t="inlineStr">
-        <is>
-          <t>LTC2 Français
+      <c r="C52" s="29" t="inlineStr">
+        <is>
+          <t>Pétrographie et Minéralogie
 (CM - Amphi 1)
 Section: GEG S4</t>
         </is>
       </c>
-      <c r="H52" s="19" t="inlineStr">
-        <is>
-          <t>Méthodes d'analyse
-(CM - Amphi 2)
-Section: GEG S4</t>
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="25" t="n"/>
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="18" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(TD - Salle 26)
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="H52" s="23" t="inlineStr">
+        <is>
+          <t>Géologie Structurale
+(TD - Salle 28)
+GEG S4 - Groupe: 1</t>
         </is>
       </c>
     </row>
@@ -9315,13 +9388,13 @@
           <t>SAMEDI</t>
         </is>
       </c>
-      <c r="B64" s="21" t="n"/>
-      <c r="C64" s="21" t="n"/>
+      <c r="B64" s="25" t="n"/>
+      <c r="C64" s="25" t="n"/>
       <c r="D64" s="20" t="n"/>
-      <c r="E64" s="21" t="n"/>
+      <c r="E64" s="25" t="n"/>
       <c r="F64" s="20" t="n"/>
-      <c r="G64" s="21" t="n"/>
-      <c r="H64" s="21" t="n"/>
+      <c r="G64" s="25" t="n"/>
+      <c r="H64" s="25" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
@@ -9548,25 +9621,13 @@
           <t>LUNDI</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n"/>
-      <c r="C4" s="23" t="inlineStr">
-        <is>
-          <t>Métrologie Capteurs
-(CM - Amphi 3)
-Section: GESE S4</t>
-        </is>
-      </c>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
       <c r="D4" s="20" t="n"/>
-      <c r="E4" s="21" t="n"/>
+      <c r="E4" s="25" t="n"/>
       <c r="F4" s="20" t="n"/>
-      <c r="G4" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(TD - Salle 30)
-GESE S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H4" s="21" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n"/>
@@ -9684,25 +9745,31 @@
           <t>MARDI</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>Métrologie Capteurs
+      <c r="B16" s="25" t="n"/>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>Electrotechnique
 (TD - Salle 27)
 GESE S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="C16" s="29" t="inlineStr">
-        <is>
-          <t>Automatique
-(CM - Amphi 4)
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(CM - Amphi 2)
 Section: GESE S4</t>
         </is>
       </c>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="21" t="n"/>
       <c r="F16" s="20" t="n"/>
-      <c r="G16" s="21" t="n"/>
-      <c r="H16" s="21" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 23)
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
@@ -9820,29 +9887,23 @@
           <t>MERCREDI</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n"/>
-      <c r="C28" s="29" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>Analyse Numérique
 (CM - Amphi 2)
 Section: GESE S4</t>
         </is>
       </c>
+      <c r="C28" s="25" t="n"/>
       <c r="D28" s="20" t="n"/>
-      <c r="E28" s="21" t="n"/>
+      <c r="E28" s="25" t="n"/>
       <c r="F28" s="20" t="n"/>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G28" s="25" t="n"/>
+      <c r="H28" s="24" t="inlineStr">
         <is>
           <t>Structure des Données
-(TD - Salle 28)
-GESE S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H28" s="29" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
-(TD - Salle 23)
-GESE S4 - Groupe: 1</t>
+(CM - Amphi 2)
+Section: GESE S4</t>
         </is>
       </c>
     </row>
@@ -9962,28 +10023,34 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="21" t="n"/>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>Automatique
+(TD - Salle 24)
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>LTC2 Français
-(TD - Salle 30)
+          <t>Structure des Données
+(TD - Salle 28)
 GESE S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="D40" s="20" t="n"/>
-      <c r="E40" s="18" t="inlineStr">
+      <c r="E40" s="25" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="24" t="inlineStr">
+        <is>
+          <t>Métrologie Capteurs
+(TD - Salle 27)
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
         <is>
           <t>Développement Personnel
-(CM - Amphi 1)
-Section: GESE S4</t>
-        </is>
-      </c>
-      <c r="F40" s="20" t="n"/>
-      <c r="G40" s="21" t="n"/>
-      <c r="H40" s="19" t="inlineStr">
-        <is>
-          <t>Electrotechnique
-(TD - Salle 23)
+(TD - Salle 24)
 GESE S4 - Groupe: 1</t>
         </is>
       </c>
@@ -10104,37 +10171,43 @@
           <t>VENDREDI</t>
         </is>
       </c>
-      <c r="B52" s="19" t="inlineStr">
-        <is>
-          <t>Electrotechnique
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(CM - Amphi 1)
+Section: GESE S4</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>Métrologie Capteurs
+(CM - Amphi 3)
+Section: GESE S4</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="26" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
+(TD - Salle 24)
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="21" t="inlineStr">
+        <is>
+          <t>Automatique
 (CM - Amphi 4)
 Section: GESE S4</t>
         </is>
       </c>
-      <c r="C52" s="22" t="inlineStr">
-        <is>
-          <t>Structure des Données
-(CM - Amphi 1)
+      <c r="H52" s="23" t="inlineStr">
+        <is>
+          <t>Electrotechnique
+(CM - Amphi 3)
 Section: GESE S4</t>
         </is>
       </c>
-      <c r="D52" s="20" t="n"/>
-      <c r="E52" s="24" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(CM - Amphi 1)
-Section: GESE S4</t>
-        </is>
-      </c>
-      <c r="F52" s="20" t="n"/>
-      <c r="G52" s="29" t="inlineStr">
-        <is>
-          <t>Automatique
-(TD - Salle 23)
-GESE S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H52" s="21" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n"/>
@@ -10252,13 +10325,13 @@
           <t>SAMEDI</t>
         </is>
       </c>
-      <c r="B64" s="21" t="n"/>
-      <c r="C64" s="21" t="n"/>
+      <c r="B64" s="25" t="n"/>
+      <c r="C64" s="25" t="n"/>
       <c r="D64" s="20" t="n"/>
-      <c r="E64" s="21" t="n"/>
+      <c r="E64" s="25" t="n"/>
       <c r="F64" s="20" t="n"/>
-      <c r="G64" s="21" t="n"/>
-      <c r="H64" s="21" t="n"/>
+      <c r="G64" s="25" t="n"/>
+      <c r="H64" s="25" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
@@ -10485,37 +10558,31 @@
           <t>LUNDI</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
-(CM - Amphi 2)
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>Structure des Données
+(TD - Salle 30)
+GI S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>Systèmes d'Information et Bases de Données
+(CM - Amphi 4)
 Section: GI S4</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(TD - Salle 26)
-GI S4 - Groupe: 1</t>
-        </is>
-      </c>
       <c r="D4" s="20" t="n"/>
-      <c r="E4" s="21" t="n"/>
+      <c r="E4" s="25" t="n"/>
       <c r="F4" s="20" t="n"/>
-      <c r="G4" s="26" t="inlineStr">
-        <is>
-          <t>Programmation Web
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t>Systèmes d'Information et Bases de Données
 (TD - Salle 29)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="H4" s="22" t="inlineStr">
-        <is>
-          <t>Structure des Données
-(TD - Salle 28)
 GI S4 - Groupe: 2</t>
         </is>
       </c>
+      <c r="H4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n"/>
@@ -10554,7 +10621,13 @@
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>Recherche Opérationnelle
+(TD - Salle 27)
+GI S4 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="H8" s="7" t="n"/>
     </row>
     <row r="9">
@@ -10569,25 +10642,19 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>Systèmes d'Information et Bases de Données
-(TD - Salle 28)
+(TD - Salle 29)
 GI S4 - Groupe: 3</t>
         </is>
       </c>
+      <c r="C10" s="7" t="n"/>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(TD - Salle 23)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
+      <c r="H10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -10606,7 +10673,13 @@
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 28)
+GI S4 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="H12" s="7" t="n"/>
     </row>
     <row r="13">
@@ -10645,29 +10718,35 @@
           <t>MARDI</t>
         </is>
       </c>
-      <c r="B16" s="21" t="n"/>
-      <c r="C16" s="29" t="inlineStr">
+      <c r="B16" s="25" t="n"/>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>Recherche Opérationnelle
+(TD - Salle 28)
+GI S4 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(CM - Amphi 2)
+Section: GI S4</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 24)
+GI S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="H16" s="26" t="inlineStr">
         <is>
           <t>Analyse Numérique
 (TD - Salle 24)
 GI S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="21" t="n"/>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="24" t="inlineStr">
-        <is>
-          <t>Recherche Opérationnelle
-(TD - Salle 25)
-GI S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>Recherche Opérationnelle
-(TD - Salle 25)
-GI S4 - Groupe: 3</t>
         </is>
       </c>
     </row>
@@ -10709,13 +10788,7 @@
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="22" t="inlineStr">
-        <is>
-          <t>Structure des Données
-(TD - Salle 23)
-GI S4 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="H20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n"/>
@@ -10730,11 +10803,11 @@
     <row r="22">
       <c r="A22" s="7" t="n"/>
       <c r="B22" s="7" t="n"/>
-      <c r="C22" s="22" t="inlineStr">
-        <is>
-          <t>Structure des Données
-(TD - Salle 28)
-GI S4 - Groupe: 3</t>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>Systèmes d'Information et Bases de Données
+(TD - Salle 29)
+GI S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="D22" s="7" t="n"/>
@@ -10761,13 +10834,7 @@
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
-      <c r="H24" s="29" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
-(TD - Salle 24)
-GI S4 - Groupe: 2</t>
-        </is>
-      </c>
+      <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
@@ -10805,35 +10872,35 @@
           <t>MERCREDI</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t>Recherche Opérationnelle
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
 (CM - Amphi 2)
 Section: GI S4</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 26)
+GI S4 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>Programmation Web
-(TD - Salle 29)
-GI S4 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="21" t="n"/>
-      <c r="F28" s="20" t="n"/>
-      <c r="G28" s="29" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
-(TD - Salle 23)
+(TD - Salle 30)
 GI S4 - Groupe: 3</t>
         </is>
       </c>
       <c r="H28" s="24" t="inlineStr">
         <is>
-          <t>Recherche Opérationnelle
-(TD - Salle 25)
-GI S4 - Groupe: 2</t>
+          <t>Structure des Données
+(CM - Amphi 2)
+Section: GI S4</t>
         </is>
       </c>
     </row>
@@ -10890,10 +10957,10 @@
     <row r="34">
       <c r="A34" s="7" t="n"/>
       <c r="B34" s="7" t="n"/>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(TD - Salle 24)
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 28)
 GI S4 - Groupe: 1</t>
         </is>
       </c>
@@ -10959,41 +11026,35 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(TD - Salle 24)
-GI S4 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="C40" s="28" t="inlineStr">
-        <is>
-          <t>Systèmes d'Information et Bases de Données
-(CM - Amphi 1)
-Section: GI S4</t>
+      <c r="B40" s="25" t="n"/>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>Programmation Web
+(TD - Salle 30)
+GI S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="D40" s="20" t="n"/>
-      <c r="E40" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(CM - Amphi 1)
-Section: GI S4</t>
-        </is>
-      </c>
-      <c r="F40" s="20" t="n"/>
-      <c r="G40" s="28" t="inlineStr">
-        <is>
-          <t>Systèmes d'Information et Bases de Données
-(TD - Salle 28)
-GI S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H40" s="24" t="inlineStr">
-        <is>
-          <t>LTC2 Français
+      <c r="E40" s="24" t="inlineStr">
+        <is>
+          <t>Structure des Données
 (TD - Salle 30)
 GI S4 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="22" t="inlineStr">
+        <is>
+          <t>Programmation Web
+(CM - Amphi 4)
+Section: GI S4</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 25)
+GI S4 - Groupe: 3</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11111,13 @@
     <row r="46">
       <c r="A46" s="7" t="n"/>
       <c r="B46" s="7" t="n"/>
-      <c r="C46" s="7" t="n"/>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>Recherche Opérationnelle
+(TD - Salle 27)
+GI S4 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
@@ -11115,38 +11182,38 @@
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>LTC2 Français
-(TD - Salle 23)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="C52" s="22" t="inlineStr">
-        <is>
-          <t>Structure des Données
+          <t>Développement Personnel
 (CM - Amphi 1)
 Section: GI S4</t>
         </is>
       </c>
+      <c r="C52" s="26" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
+(TD - Salle 30)
+GI S4 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="D52" s="20" t="n"/>
       <c r="E52" s="24" t="inlineStr">
         <is>
-          <t>LTC2 Français
-(CM - Amphi 1)
+          <t>Recherche Opérationnelle
+(CM - Amphi 2)
 Section: GI S4</t>
         </is>
       </c>
       <c r="F52" s="20" t="n"/>
-      <c r="G52" s="26" t="inlineStr">
+      <c r="G52" s="22" t="inlineStr">
         <is>
           <t>Programmation Web
-(CM - Amphi 3)
-Section: GI S4</t>
-        </is>
-      </c>
-      <c r="H52" s="28" t="inlineStr">
-        <is>
-          <t>Systèmes d'Information et Bases de Données
-(TD - Salle 28)
+(TD - Salle 24)
+GI S4 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="H52" s="24" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 26)
 GI S4 - Groupe: 2</t>
         </is>
       </c>
@@ -11203,18 +11270,24 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n"/>
-      <c r="B58" s="26" t="inlineStr">
-        <is>
-          <t>Programmation Web
+      <c r="B58" s="7" t="n"/>
+      <c r="C58" s="24" t="inlineStr">
+        <is>
+          <t>Structure des Données
 (TD - Salle 29)
-GI S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="n"/>
+GI S4 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
-      <c r="G58" s="7" t="n"/>
+      <c r="G58" s="26" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
+(TD - Salle 30)
+GI S4 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="H58" s="7" t="n"/>
     </row>
     <row r="59">
@@ -11273,13 +11346,13 @@
           <t>SAMEDI</t>
         </is>
       </c>
-      <c r="B64" s="21" t="n"/>
-      <c r="C64" s="21" t="n"/>
+      <c r="B64" s="25" t="n"/>
+      <c r="C64" s="25" t="n"/>
       <c r="D64" s="20" t="n"/>
-      <c r="E64" s="21" t="n"/>
+      <c r="E64" s="25" t="n"/>
       <c r="F64" s="20" t="n"/>
-      <c r="G64" s="21" t="n"/>
-      <c r="H64" s="21" t="n"/>
+      <c r="G64" s="25" t="n"/>
+      <c r="H64" s="25" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
@@ -11392,60 +11465,61 @@
       <c r="H75" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="56">
+  <mergeCells count="57">
+    <mergeCell ref="B4:B9"/>
     <mergeCell ref="B40:B51"/>
     <mergeCell ref="C34:C39"/>
     <mergeCell ref="A4:A15"/>
-    <mergeCell ref="G4:G15"/>
-    <mergeCell ref="H4:H9"/>
+    <mergeCell ref="H16:H27"/>
     <mergeCell ref="F52:F63"/>
     <mergeCell ref="F28:F39"/>
+    <mergeCell ref="G8:G11"/>
     <mergeCell ref="B64:B75"/>
     <mergeCell ref="H28:H39"/>
     <mergeCell ref="D64:D75"/>
-    <mergeCell ref="B4:B15"/>
     <mergeCell ref="F64:F75"/>
+    <mergeCell ref="C58:C63"/>
     <mergeCell ref="A28:A39"/>
     <mergeCell ref="G16:G27"/>
-    <mergeCell ref="H10:H15"/>
     <mergeCell ref="B16:B27"/>
+    <mergeCell ref="G52:G57"/>
     <mergeCell ref="G40:G51"/>
-    <mergeCell ref="C4:C9"/>
+    <mergeCell ref="A40:A51"/>
     <mergeCell ref="E16:E27"/>
-    <mergeCell ref="A40:A51"/>
     <mergeCell ref="A52:A63"/>
-    <mergeCell ref="B52:B57"/>
-    <mergeCell ref="B58:B63"/>
     <mergeCell ref="E52:E63"/>
-    <mergeCell ref="G52:G63"/>
+    <mergeCell ref="H4:H15"/>
     <mergeCell ref="A64:A75"/>
     <mergeCell ref="C64:C75"/>
-    <mergeCell ref="C10:C15"/>
+    <mergeCell ref="E64:E75"/>
     <mergeCell ref="C16:C21"/>
-    <mergeCell ref="E64:E75"/>
     <mergeCell ref="F4:F15"/>
     <mergeCell ref="C22:C27"/>
     <mergeCell ref="D40:D51"/>
+    <mergeCell ref="C46:C51"/>
     <mergeCell ref="F40:F51"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="C4:C15"/>
     <mergeCell ref="F16:F27"/>
     <mergeCell ref="E4:E15"/>
+    <mergeCell ref="B52:B63"/>
     <mergeCell ref="D52:D63"/>
-    <mergeCell ref="H16:H19"/>
+    <mergeCell ref="G4:G7"/>
     <mergeCell ref="H64:H75"/>
+    <mergeCell ref="B10:B15"/>
+    <mergeCell ref="C40:C45"/>
+    <mergeCell ref="G58:G63"/>
     <mergeCell ref="E28:E39"/>
     <mergeCell ref="G28:G39"/>
     <mergeCell ref="H40:H51"/>
+    <mergeCell ref="C52:C57"/>
     <mergeCell ref="H52:H63"/>
     <mergeCell ref="A16:A27"/>
-    <mergeCell ref="C40:C51"/>
     <mergeCell ref="E40:E51"/>
     <mergeCell ref="D4:D15"/>
-    <mergeCell ref="C52:C63"/>
     <mergeCell ref="D16:D27"/>
     <mergeCell ref="G64:G75"/>
-    <mergeCell ref="H24:H27"/>
-    <mergeCell ref="H20:H23"/>
+    <mergeCell ref="G12:G15"/>
     <mergeCell ref="B28:B39"/>
     <mergeCell ref="C28:C33"/>
     <mergeCell ref="D28:D39"/>
@@ -11513,31 +11587,31 @@
           <t>LUNDI</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Optique Physique
 (CM - Amphi 2)
 Section: GP S4</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(TD - Salle 23)
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="27" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
+(TD - Salle 25)
 GP S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="21" t="n"/>
-      <c r="F4" s="20" t="n"/>
-      <c r="G4" s="29" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
-(TD - Salle 23)
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Optique Physique
+(TD - Salle 27)
 GP S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="H4" s="21" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n"/>
@@ -11655,19 +11729,25 @@
           <t>MARDI</t>
         </is>
       </c>
-      <c r="B16" s="21" t="n"/>
-      <c r="C16" s="21" t="n"/>
+      <c r="B16" s="25" t="n"/>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 24)
+GP S4 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="D16" s="20" t="n"/>
-      <c r="E16" s="27" t="inlineStr">
-        <is>
-          <t>Analyse 4
-(TD - Salle 25)
-GP S4 - Groupe: 1</t>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(CM - Amphi 2)
+Section: GP S4</t>
         </is>
       </c>
       <c r="F16" s="20" t="n"/>
-      <c r="G16" s="21" t="n"/>
-      <c r="H16" s="21" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
@@ -11785,25 +11865,37 @@
           <t>MERCREDI</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n"/>
-      <c r="C28" s="29" t="inlineStr">
-        <is>
-          <t>Optique Physique
-(CM - Amphi 4)
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
+(CM - Amphi 2)
 Section: GP S4</t>
         </is>
       </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>Analyse 4
+(TD - Salle 24)
+GP S4 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="D28" s="20" t="n"/>
-      <c r="E28" s="21" t="n"/>
+      <c r="E28" s="25" t="n"/>
       <c r="F28" s="20" t="n"/>
-      <c r="G28" s="27" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
-(CM - Amphi 1)
+      <c r="G28" s="26" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
+(TD - Salle 25)
+GP S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>Structure des Données
+(CM - Amphi 2)
 Section: GP S4</t>
         </is>
       </c>
-      <c r="H28" s="21" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n"/>
@@ -11921,34 +12013,28 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="27" t="inlineStr">
+      <c r="B40" s="25" t="n"/>
+      <c r="C40" s="27" t="inlineStr">
         <is>
           <t>Mécanique des Fluides et Transfert Thermique
+(CM - Amphi 2)
+Section: GP S4</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="25" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="21" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 26)
+GP S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
+        <is>
+          <t>Structure des Données
 (TD - Salle 29)
-GP S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(TD - Salle 25)
-GP S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="n"/>
-      <c r="E40" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(CM - Amphi 1)
-Section: GP S4</t>
-        </is>
-      </c>
-      <c r="F40" s="20" t="n"/>
-      <c r="G40" s="21" t="n"/>
-      <c r="H40" s="22" t="inlineStr">
-        <is>
-          <t>Structure des Données
-(TD - Salle 28)
 GP S4 - Groupe: 1</t>
         </is>
       </c>
@@ -12069,37 +12155,25 @@
           <t>VENDREDI</t>
         </is>
       </c>
-      <c r="B52" s="21" t="n"/>
-      <c r="C52" s="22" t="inlineStr">
-        <is>
-          <t>Structure des Données
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>Développement Personnel
 (CM - Amphi 1)
 Section: GP S4</t>
         </is>
       </c>
+      <c r="C52" s="25" t="n"/>
       <c r="D52" s="20" t="n"/>
-      <c r="E52" s="24" t="inlineStr">
-        <is>
-          <t>LTC2 Français
+      <c r="E52" s="25" t="n"/>
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="18" t="inlineStr">
+        <is>
+          <t>Analyse 4
 (CM - Amphi 1)
 Section: GP S4</t>
         </is>
       </c>
-      <c r="F52" s="20" t="n"/>
-      <c r="G52" s="27" t="inlineStr">
-        <is>
-          <t>Analyse 4
-(CM - Amphi 2)
-Section: GP S4</t>
-        </is>
-      </c>
-      <c r="H52" s="29" t="inlineStr">
-        <is>
-          <t>Optique Physique
-(TD - Salle 24)
-GP S4 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="H52" s="25" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n"/>
@@ -12217,13 +12291,13 @@
           <t>SAMEDI</t>
         </is>
       </c>
-      <c r="B64" s="21" t="n"/>
-      <c r="C64" s="21" t="n"/>
+      <c r="B64" s="25" t="n"/>
+      <c r="C64" s="25" t="n"/>
       <c r="D64" s="20" t="n"/>
-      <c r="E64" s="21" t="n"/>
+      <c r="E64" s="25" t="n"/>
       <c r="F64" s="20" t="n"/>
-      <c r="G64" s="21" t="n"/>
-      <c r="H64" s="21" t="n"/>
+      <c r="G64" s="25" t="n"/>
+      <c r="H64" s="25" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
@@ -12450,40 +12524,40 @@
           <t>LUNDI</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 26)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="C4" s="22" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(CM - Amphi 4)
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>Electricité
+(TD - Salle 23)
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 25)
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="29" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(CM - Amphi 1)
 Section: GP-GI S2</t>
         </is>
       </c>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="25" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
-(TD - Salle 30)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
       <c r="F4" s="20" t="n"/>
-      <c r="G4" s="24" t="inlineStr">
+      <c r="G4" s="21" t="inlineStr">
         <is>
           <t>Algèbre 2
 (CM - Amphi 1)
 Section: GP-GI S2</t>
         </is>
       </c>
-      <c r="H4" s="25" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
-(CM - Amphi 1)
+      <c r="H4" s="26" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(CM - Amphi 4)
 Section: GP-GI S2</t>
         </is>
       </c>
@@ -12510,29 +12584,23 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 27)
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="C7" s="7" t="n"/>
       <c r="D7" s="7" t="n"/>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 29)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n"/>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 24)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
+      <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
@@ -12552,16 +12620,22 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 28)
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 27)
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="D10" s="7" t="n"/>
-      <c r="E10" s="24" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 26)
-GP-GI S2 - Groupe: 4</t>
-        </is>
-      </c>
+      <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="n"/>
@@ -12578,13 +12652,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n"/>
-      <c r="B12" s="28" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 25)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
+      <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
@@ -12594,16 +12662,16 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 26)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="n"/>
-      <c r="E13" s="28" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 27)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
       <c r="H13" s="7" t="n"/>
@@ -12634,41 +12702,41 @@
           <t>MARDI</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 24)
-GP-GI S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="C16" s="29" t="inlineStr">
-        <is>
-          <t>Analyse 2
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
 (CM - Amphi 1)
 Section: GP-GI S2</t>
         </is>
       </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(CM - Amphi 4)
+Section: GP-GI S2</t>
+        </is>
+      </c>
       <c r="D16" s="20" t="n"/>
-      <c r="E16" s="25" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
-(TD - Salle 26)
-GP-GI S2 - Groupe: 5</t>
+      <c r="E16" s="29" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 27)
+GP-GI S2 - Groupe: 4</t>
         </is>
       </c>
       <c r="F16" s="20" t="n"/>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="26" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 23)
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="H16" s="26" t="inlineStr">
         <is>
           <t>Langue Etrangère 2
-(TD - Salle 27)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="H16" s="28" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(CM - Amphi 2)
-Section: GP-GI S2</t>
+(TD - Salle 30)
+GP-GI S2 - Groupe: 6</t>
         </is>
       </c>
     </row>
@@ -12704,25 +12772,19 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n"/>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 26)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
+      <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="7" t="n"/>
-      <c r="E20" s="29" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 23)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 27)
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n"/>
@@ -12739,13 +12801,19 @@
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
+      <c r="E22" s="29" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 29)
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="F22" s="7" t="n"/>
-      <c r="G22" s="22" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 28)
-GP-GI S2 - Groupe: 5</t>
+      <c r="G22" s="26" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 27)
+GP-GI S2 - Groupe: 1</t>
         </is>
       </c>
       <c r="H22" s="7" t="n"/>
@@ -12762,25 +12830,19 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
-      <c r="B24" s="22" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 25)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>Electricité
-(TD - Salle 27)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>Electricité
+(TD - Salle 28)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
@@ -12818,41 +12880,41 @@
           <t>MERCREDI</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 25)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 28)
-GP-GI S2 - Groupe: 5</t>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>Electricité
+(TD - Salle 23)
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
+(TD - Salle 29)
+GP-GI S2 - Groupe: 6</t>
         </is>
       </c>
       <c r="D28" s="20" t="n"/>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>Langue Etrangère 2
-(TD - Salle 25)
-GP-GI S2 - Groupe: 4</t>
+          <t>Electricité
+(CM - Amphi 4)
+Section: GP-GI S2</t>
         </is>
       </c>
       <c r="F28" s="20" t="n"/>
-      <c r="G28" s="28" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 29)
-GP-GI S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="H28" s="23" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(CM - Amphi 1)
-Section: GP-GI S2</t>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 27)
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
+(TD - Salle 23)
+GP-GI S2 - Groupe: 3</t>
         </is>
       </c>
     </row>
@@ -12881,13 +12943,7 @@
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="n"/>
-      <c r="E31" s="28" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 26)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
       <c r="H31" s="7" t="n"/>
@@ -12914,31 +12970,37 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n"/>
-      <c r="B34" s="25" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
+      <c r="B34" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
 (TD - Salle 26)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="C34" s="29" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 27)
-GP-GI S2 - Groupe: 2</t>
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>Electricité
+(TD - Salle 23)
+GP-GI S2 - Groupe: 4</t>
         </is>
       </c>
       <c r="D34" s="7" t="n"/>
-      <c r="E34" s="23" t="inlineStr">
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="21" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 23)
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="H34" s="26" t="inlineStr">
         <is>
           <t>Structure de la matière
-(TD - Salle 30)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
+(TD - Salle 25)
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n"/>
@@ -12965,13 +13027,7 @@
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="n"/>
-      <c r="E37" s="28" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 27)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
       <c r="H37" s="7" t="n"/>
@@ -13002,35 +13058,41 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="19" t="inlineStr">
-        <is>
-          <t>Electricité
+      <c r="B40" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(CM - Amphi 4)
+Section: GP-GI S2</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 23)
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="29" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 29)
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="26" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 29)
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="H40" s="26" t="inlineStr">
+        <is>
+          <t>Culture digitale
 (TD - Salle 27)
 GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="C40" s="29" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 23)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="n"/>
-      <c r="E40" s="21" t="n"/>
-      <c r="F40" s="20" t="n"/>
-      <c r="G40" s="19" t="inlineStr">
-        <is>
-          <t>Electricité
-(TD - Salle 23)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="H40" s="19" t="inlineStr">
-        <is>
-          <t>Electricité
-(CM - Amphi 2)
-Section: GP-GI S2</t>
         </is>
       </c>
     </row>
@@ -13066,22 +13128,16 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n"/>
-      <c r="B44" s="29" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 26)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
       <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
-      <c r="G44" s="24" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 26)
-GP-GI S2 - Groupe: 6</t>
+      <c r="G44" s="26" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 23)
+GP-GI S2 - Groupe: 1</t>
         </is>
       </c>
       <c r="H44" s="7" t="n"/>
@@ -13099,18 +13155,30 @@
     <row r="46">
       <c r="A46" s="7" t="n"/>
       <c r="B46" s="7" t="n"/>
-      <c r="C46" s="23" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 29)
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 24)
 GP-GI S2 - Groupe: 2</t>
         </is>
       </c>
       <c r="D46" s="7" t="n"/>
-      <c r="E46" s="7" t="n"/>
+      <c r="E46" s="21" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 27)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
-      <c r="H46" s="7" t="n"/>
+      <c r="H46" s="21" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
+(TD - Salle 23)
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n"/>
@@ -13124,22 +13192,16 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
-      <c r="B48" s="25" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
-(TD - Salle 30)
-GP-GI S2 - Groupe: 4</t>
-        </is>
-      </c>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
-      <c r="G48" s="23" t="inlineStr">
+      <c r="G48" s="26" t="inlineStr">
         <is>
           <t>Structure de la matière
-(TD - Salle 24)
-GP-GI S2 - Groupe: 5</t>
+(TD - Salle 28)
+GP-GI S2 - Groupe: 2</t>
         </is>
       </c>
       <c r="H48" s="7" t="n"/>
@@ -13180,34 +13242,40 @@
           <t>VENDREDI</t>
         </is>
       </c>
-      <c r="B52" s="21" t="n"/>
-      <c r="C52" s="22" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 25)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="D52" s="20" t="n"/>
-      <c r="E52" s="29" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 30)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="F52" s="20" t="n"/>
-      <c r="G52" s="19" t="inlineStr">
-        <is>
-          <t>Electricité
-(TD - Salle 27)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="H52" s="25" t="inlineStr">
+      <c r="B52" s="21" t="inlineStr">
         <is>
           <t>Circuits électriques et électronique
 (TD - Salle 29)
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="C52" s="26" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 24)
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="21" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
+(TD - Salle 23)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 23)
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="H52" s="26" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 25)
 GP-GI S2 - Groupe: 6</t>
         </is>
       </c>
@@ -13237,31 +13305,31 @@
       <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
-      <c r="E55" s="19" t="inlineStr">
-        <is>
-          <t>Electricité
-(TD - Salle 23)
-GP-GI S2 - Groupe: 4</t>
-        </is>
-      </c>
+      <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
-      <c r="H55" s="7" t="n"/>
+      <c r="H55" s="29" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 29)
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n"/>
       <c r="B56" s="7" t="n"/>
-      <c r="C56" s="19" t="inlineStr">
-        <is>
-          <t>Electricité
-(TD - Salle 27)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
+      <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
-      <c r="G56" s="7" t="n"/>
+      <c r="G56" s="22" t="inlineStr">
+        <is>
+          <t>Electricité
+(TD - Salle 28)
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
       <c r="H56" s="7" t="n"/>
     </row>
     <row r="57">
@@ -13276,23 +13344,29 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n"/>
-      <c r="B58" s="7" t="n"/>
-      <c r="C58" s="7" t="n"/>
+      <c r="B58" s="21" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
+(TD - Salle 23)
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="C58" s="22" t="inlineStr">
+        <is>
+          <t>Electricité
+(TD - Salle 28)
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="D58" s="7" t="n"/>
-      <c r="E58" s="28" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 24)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
+      <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
-      <c r="H58" s="29" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 27)
-GP-GI S2 - Groupe: 4</t>
+      <c r="H58" s="21" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 23)
+GP-GI S2 - Groupe: 1</t>
         </is>
       </c>
     </row>
@@ -13309,17 +13383,17 @@
     <row r="60">
       <c r="A60" s="7" t="n"/>
       <c r="B60" s="7" t="n"/>
-      <c r="C60" s="25" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
-(TD - Salle 30)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
+      <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
-      <c r="G60" s="7" t="n"/>
+      <c r="G60" s="26" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 27)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="H60" s="7" t="n"/>
     </row>
     <row r="61">
@@ -13327,16 +13401,16 @@
       <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="7" t="n"/>
-      <c r="E61" s="23" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 29)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
-      <c r="H61" s="7" t="n"/>
+      <c r="H61" s="29" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 30)
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n"/>
@@ -13364,13 +13438,13 @@
           <t>SAMEDI</t>
         </is>
       </c>
-      <c r="B64" s="21" t="n"/>
-      <c r="C64" s="21" t="n"/>
+      <c r="B64" s="25" t="n"/>
+      <c r="C64" s="25" t="n"/>
       <c r="D64" s="20" t="n"/>
-      <c r="E64" s="21" t="n"/>
+      <c r="E64" s="25" t="n"/>
       <c r="F64" s="20" t="n"/>
-      <c r="G64" s="21" t="n"/>
-      <c r="H64" s="21" t="n"/>
+      <c r="G64" s="25" t="n"/>
+      <c r="H64" s="25" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
@@ -13483,82 +13557,80 @@
       <c r="H75" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="75">
+  <mergeCells count="73">
+    <mergeCell ref="B40:B51"/>
     <mergeCell ref="C34:C39"/>
     <mergeCell ref="A4:A15"/>
     <mergeCell ref="G4:G15"/>
-    <mergeCell ref="H16:H27"/>
+    <mergeCell ref="G52:G55"/>
     <mergeCell ref="F52:F63"/>
     <mergeCell ref="F28:F39"/>
-    <mergeCell ref="B12:B15"/>
     <mergeCell ref="B64:B75"/>
-    <mergeCell ref="H28:H39"/>
     <mergeCell ref="D64:D75"/>
-    <mergeCell ref="E20:E23"/>
     <mergeCell ref="F64:F75"/>
+    <mergeCell ref="C58:C63"/>
     <mergeCell ref="A28:A39"/>
+    <mergeCell ref="B16:B27"/>
     <mergeCell ref="G48:G51"/>
+    <mergeCell ref="C4:C9"/>
     <mergeCell ref="A40:A51"/>
     <mergeCell ref="A52:A63"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="H58:H63"/>
-    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="H34:H39"/>
+    <mergeCell ref="B52:B57"/>
+    <mergeCell ref="B58:B63"/>
     <mergeCell ref="H4:H15"/>
-    <mergeCell ref="G52:G63"/>
+    <mergeCell ref="E52:E63"/>
     <mergeCell ref="A64:A75"/>
-    <mergeCell ref="E52:E54"/>
-    <mergeCell ref="C56:C59"/>
     <mergeCell ref="C64:C75"/>
+    <mergeCell ref="C10:C15"/>
+    <mergeCell ref="B7:B9"/>
     <mergeCell ref="E64:E75"/>
-    <mergeCell ref="E37:E39"/>
+    <mergeCell ref="G34:G39"/>
+    <mergeCell ref="H46:H51"/>
+    <mergeCell ref="H40:H45"/>
     <mergeCell ref="F4:F15"/>
-    <mergeCell ref="E55:E57"/>
-    <mergeCell ref="E61:E63"/>
-    <mergeCell ref="B48:B51"/>
+    <mergeCell ref="G28:G33"/>
+    <mergeCell ref="E46:E51"/>
     <mergeCell ref="D40:D51"/>
-    <mergeCell ref="E58:E60"/>
+    <mergeCell ref="H61:H63"/>
     <mergeCell ref="C46:C51"/>
     <mergeCell ref="F40:F51"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B44:B47"/>
-    <mergeCell ref="H52:H57"/>
-    <mergeCell ref="C52:C55"/>
-    <mergeCell ref="B40:B43"/>
-    <mergeCell ref="C4:C15"/>
+    <mergeCell ref="E40:E45"/>
     <mergeCell ref="F16:F27"/>
-    <mergeCell ref="B52:B63"/>
+    <mergeCell ref="E4:E15"/>
     <mergeCell ref="D52:D63"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="C60:C63"/>
+    <mergeCell ref="H16:H19"/>
     <mergeCell ref="B34:B39"/>
     <mergeCell ref="H64:H75"/>
     <mergeCell ref="C40:C45"/>
-    <mergeCell ref="E16:E19"/>
+    <mergeCell ref="B28:B33"/>
     <mergeCell ref="C16:C27"/>
-    <mergeCell ref="B28:B33"/>
-    <mergeCell ref="G40:G43"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="G28:G39"/>
-    <mergeCell ref="H40:H51"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="E28:E39"/>
+    <mergeCell ref="H55:H57"/>
+    <mergeCell ref="C52:C57"/>
+    <mergeCell ref="H28:H33"/>
+    <mergeCell ref="H58:H60"/>
     <mergeCell ref="A16:A27"/>
     <mergeCell ref="G44:G47"/>
-    <mergeCell ref="E40:E51"/>
+    <mergeCell ref="G60:G63"/>
+    <mergeCell ref="H52:H54"/>
+    <mergeCell ref="B10:B12"/>
     <mergeCell ref="D4:D15"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="G56:G59"/>
+    <mergeCell ref="B13:B15"/>
     <mergeCell ref="D16:D27"/>
     <mergeCell ref="G64:G75"/>
+    <mergeCell ref="E16:E21"/>
+    <mergeCell ref="H24:H27"/>
+    <mergeCell ref="H20:H23"/>
     <mergeCell ref="G16:G21"/>
     <mergeCell ref="C28:C33"/>
     <mergeCell ref="D28:D39"/>
-    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="E22:E27"/>
     <mergeCell ref="G22:G27"/>
-    <mergeCell ref="E24:E27"/>
+    <mergeCell ref="G40:G43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
